--- a/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2562.84</v>
+        <v>41189.04</v>
       </c>
       <c r="C4" t="n">
-        <v>550368</v>
+        <v>6258672</v>
       </c>
       <c r="D4" t="n">
-        <v>432432</v>
+        <v>4917528</v>
       </c>
       <c r="E4" t="n">
-        <v>124200</v>
+        <v>1420200</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>6270</v>
+        <v>115410</v>
       </c>
       <c r="H4" t="n">
-        <v>180</v>
+        <v>12900</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19170</v>
+        <v>276750</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3663.81</v>
+        <v>37371.87</v>
       </c>
       <c r="C5" t="n">
-        <v>570528</v>
+        <v>3286584</v>
       </c>
       <c r="D5" t="n">
-        <v>448272</v>
+        <v>2582316</v>
       </c>
       <c r="E5" t="n">
-        <v>90000</v>
+        <v>431100</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>9450</v>
+        <v>85050</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>9930</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>23580</v>
+        <v>183360</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3591.45</v>
+        <v>20035.53</v>
       </c>
       <c r="C6" t="n">
-        <v>342216</v>
+        <v>1279152</v>
       </c>
       <c r="D6" t="n">
-        <v>268884</v>
+        <v>1005048</v>
       </c>
       <c r="E6" t="n">
-        <v>52200</v>
+        <v>75600</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>5910</v>
+        <v>28620</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>16560</v>
+        <v>67230</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2354.04</v>
+        <v>4628.43</v>
       </c>
       <c r="C7" t="n">
-        <v>161280</v>
+        <v>327096</v>
       </c>
       <c r="D7" t="n">
-        <v>126720</v>
+        <v>257004</v>
       </c>
       <c r="E7" t="n">
-        <v>20700</v>
+        <v>13500</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7530</v>
+      </c>
+      <c r="H7" t="n">
+        <v>210</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>4710</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6630</v>
+        <v>31140</v>
       </c>
     </row>
     <row r="8">
@@ -9995,22 +9989,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1264.86</v>
+        <v>976.05</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>77112</v>
       </c>
       <c r="D8" t="n">
-        <v>41184</v>
+        <v>60588</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3600</v>
+        <v>8880</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>619.11</v>
+        <v>234.9</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>13608</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>10692</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>900</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>450</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>750</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="10">
@@ -10071,7 +10065,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>382.05</v>
+        <v>142.47</v>
       </c>
       <c r="C10" t="n">
         <v>2016</v>
@@ -10086,10 +10080,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>450</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.1</v>
+        <v>50.94</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>2016</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>1584</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="12">
@@ -10147,13 +10141,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>24.57</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>396</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10162,7 +10156,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.39</v>
+        <v>8.1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14">
@@ -10223,13 +10217,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>6.66</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>4032</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>3168</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10238,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>3720</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>1.71</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0.18</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10375,7 +10369,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,16 +11739,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1648.71</v>
+        <v>16817.34</v>
       </c>
       <c r="C5" t="n">
-        <v>313790.4</v>
+        <v>1807621.2</v>
       </c>
       <c r="D5" t="n">
-        <v>148378.03</v>
+        <v>854746.6</v>
       </c>
       <c r="E5" t="n">
-        <v>9927</v>
+        <v>47550.33</v>
       </c>
       <c r="F5" t="n">
         <v>0.12</v>
@@ -11763,19 +11757,19 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3574.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4951.8</v>
+        <v>38505.6</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2873.16</v>
+        <v>16028.42</v>
       </c>
       <c r="C6" t="n">
-        <v>307994.4</v>
+        <v>1151236.8</v>
       </c>
       <c r="D6" t="n">
-        <v>136324.19</v>
+        <v>509559.34</v>
       </c>
       <c r="E6" t="n">
-        <v>8821.799999999999</v>
+        <v>12776.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>295.5</v>
+        <v>1431</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>530.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6127.2</v>
+        <v>24875.1</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2236.34</v>
+        <v>4397.01</v>
       </c>
       <c r="C7" t="n">
-        <v>161280</v>
+        <v>327096</v>
       </c>
       <c r="D7" t="n">
-        <v>80847.36</v>
+        <v>163968.55</v>
       </c>
       <c r="E7" t="n">
-        <v>4402.89</v>
+        <v>2871.45</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>706.5</v>
+        <v>1129.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>153.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3978</v>
+        <v>18684</v>
       </c>
     </row>
     <row r="8">
@@ -11859,22 +11853,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1264.86</v>
+        <v>976.05</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>77112</v>
       </c>
       <c r="D8" t="n">
-        <v>30311.42</v>
+        <v>44592.77</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>441.54</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>916.5</v>
+        <v>643.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11889,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2556</v>
+        <v>6304.8</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>619.11</v>
+        <v>234.9</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>13608</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>8585.68</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>240.93</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>382.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>607.5</v>
+        <v>3086.1</v>
       </c>
     </row>
     <row r="10">
@@ -11935,7 +11929,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>382.05</v>
+        <v>142.47</v>
       </c>
       <c r="C10" t="n">
         <v>2016</v>
@@ -11950,10 +11944,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>400.5</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.1</v>
+        <v>50.94</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>2016</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>1423.22</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="12">
@@ -12011,13 +12005,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>24.57</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>367.09</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12026,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.39</v>
+        <v>8.1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1504.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14">
@@ -12087,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>6.66</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>4032</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>3079.3</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12102,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>3720</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>1.71</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>780.91</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0.18</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12239,7 +12233,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,16 +12671,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3627171.9</v>
+        <v>36998151.3</v>
       </c>
       <c r="C5" t="n">
-        <v>17258472</v>
+        <v>99419166</v>
       </c>
       <c r="D5" t="n">
-        <v>15035145.98</v>
+        <v>86611472.56999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1828950.48</v>
+        <v>8760672.800000001</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -12695,19 +12689,19 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>988968.42</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>46645.96</v>
+        <v>362722.75</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6320952</v>
+        <v>35262532.8</v>
       </c>
       <c r="C6" t="n">
-        <v>16939692</v>
+        <v>63318024</v>
       </c>
       <c r="D6" t="n">
-        <v>13813729.97</v>
+        <v>51633647.52</v>
       </c>
       <c r="E6" t="n">
-        <v>1625328.43</v>
+        <v>2353923.94</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5466.75</v>
+        <v>26473.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>146652.16</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>29166.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>57718.22</v>
+        <v>234323.44</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4919943.6</v>
+        <v>9673418.699999999</v>
       </c>
       <c r="C7" t="n">
-        <v>8870400</v>
+        <v>17990280</v>
       </c>
       <c r="D7" t="n">
-        <v>8192262.99</v>
+        <v>16614933.37</v>
       </c>
       <c r="E7" t="n">
-        <v>811188.45</v>
+        <v>529035.95</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13070.25</v>
+        <v>20895.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>42410.44</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>40833.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>37472.76</v>
+        <v>176003.28</v>
       </c>
     </row>
     <row r="8">
@@ -12791,22 +12785,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2782692</v>
+        <v>2147310</v>
       </c>
       <c r="C8" t="n">
-        <v>2882880</v>
+        <v>4241160</v>
       </c>
       <c r="D8" t="n">
-        <v>3071456.59</v>
+        <v>4518585.18</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>81349.33</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16955.25</v>
+        <v>11904.75</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12821,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>24077.52</v>
+        <v>59391.22</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1362042</v>
+        <v>516780</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>748440</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>869986.55</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>44388.94</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>7076.25</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5722.65</v>
+        <v>29071.06</v>
       </c>
     </row>
     <row r="10">
@@ -12867,7 +12861,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>840510</v>
+        <v>313434</v>
       </c>
       <c r="C10" t="n">
         <v>110880</v>
@@ -12882,10 +12876,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>6105</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3772.71</v>
+        <v>27666.54</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>473220</v>
+        <v>112068</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>110880</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>144215.29</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>4995</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>22890.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,13 +12937,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345510</v>
+        <v>54054</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>27720</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>37197.43</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12958,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>3885</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>10456.2</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>370458</v>
+        <v>17820</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>152401.13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>2220</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="14">
@@ -13019,13 +13013,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94248</v>
+        <v>14652</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>221760</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>312025.06</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13034,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>68820</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>3762</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>79129.81</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>396</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13171,7 +13165,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>160506.72</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>41189.04</v>
+        <v>15260.4</v>
       </c>
       <c r="C4" t="n">
-        <v>6258672</v>
+        <v>1675800</v>
       </c>
       <c r="D4" t="n">
-        <v>4917528</v>
+        <v>1316700</v>
       </c>
       <c r="E4" t="n">
-        <v>1420200</v>
+        <v>699300</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>115410</v>
+        <v>46620</v>
       </c>
       <c r="H4" t="n">
-        <v>12900</v>
+        <v>3840</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>276750</v>
+        <v>164520</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>37371.87</v>
+        <v>2992.05</v>
       </c>
       <c r="C5" t="n">
-        <v>3286584</v>
+        <v>291312</v>
       </c>
       <c r="D5" t="n">
-        <v>2582316</v>
+        <v>228888</v>
       </c>
       <c r="E5" t="n">
-        <v>431100</v>
+        <v>145800</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>85050</v>
+        <v>9060</v>
       </c>
       <c r="H5" t="n">
-        <v>9930</v>
+        <v>780</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>183360</v>
+        <v>42210</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>20035.53</v>
+        <v>260.73</v>
       </c>
       <c r="C6" t="n">
-        <v>1279152</v>
+        <v>40824</v>
       </c>
       <c r="D6" t="n">
-        <v>1005048</v>
+        <v>32076</v>
       </c>
       <c r="E6" t="n">
-        <v>75600</v>
+        <v>10800</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>28620</v>
+        <v>420</v>
       </c>
       <c r="H6" t="n">
-        <v>930</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>67230</v>
+        <v>7530</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4628.43</v>
+        <v>74.7</v>
       </c>
       <c r="C7" t="n">
-        <v>327096</v>
+        <v>6048</v>
       </c>
       <c r="D7" t="n">
-        <v>257004</v>
+        <v>4752</v>
       </c>
       <c r="E7" t="n">
-        <v>13500</v>
+        <v>1800</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>7530</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>31140</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
@@ -13723,22 +13717,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>976.05</v>
+        <v>1.62</v>
       </c>
       <c r="C8" t="n">
-        <v>77112</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>60588</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -13753,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8880</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>234.9</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>13608</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>10692</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>450</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3810</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13799,13 +13793,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>142.47</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13814,10 +13808,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>50.94</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2430</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -13875,13 +13869,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>24.57</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13890,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,13 +13945,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>4032</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3168</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13966,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14068,10 +14062,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>16817.34</v>
+        <v>1346.42</v>
       </c>
       <c r="C5" t="n">
-        <v>1807621.2</v>
+        <v>160221.6</v>
       </c>
       <c r="D5" t="n">
-        <v>854746.6</v>
+        <v>75761.92999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>47550.33</v>
+        <v>16081.74</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3574.8</v>
+        <v>280.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>38505.6</v>
+        <v>8864.1</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>16028.42</v>
+        <v>208.58</v>
       </c>
       <c r="C6" t="n">
-        <v>1151236.8</v>
+        <v>36741.6</v>
       </c>
       <c r="D6" t="n">
-        <v>509559.34</v>
+        <v>16262.53</v>
       </c>
       <c r="E6" t="n">
-        <v>12776.4</v>
+        <v>1825.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1431</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>530.1</v>
+        <v>119.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>24875.1</v>
+        <v>2786.1</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4397.01</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>327096</v>
+        <v>6048</v>
       </c>
       <c r="D7" t="n">
-        <v>163968.55</v>
+        <v>3031.78</v>
       </c>
       <c r="E7" t="n">
-        <v>2871.45</v>
+        <v>382.86</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1129.5</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>153.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18684</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
@@ -14655,22 +14649,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>976.05</v>
+        <v>1.62</v>
       </c>
       <c r="C8" t="n">
-        <v>77112</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>44592.77</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>441.54</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>643.5</v>
+        <v>19.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14685,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6304.8</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>234.9</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>13608</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>8585.68</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>240.93</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>382.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3086.1</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14731,13 +14725,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>142.47</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14746,10 +14740,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2937</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>50.94</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1423.22</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2430</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -14807,13 +14801,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>24.57</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>367.09</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14822,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1504.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,13 +14877,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>4032</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3079.3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14898,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>780.91</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -15000,10 +14994,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>36998151.3</v>
+        <v>2962129.5</v>
       </c>
       <c r="C5" t="n">
-        <v>99419166</v>
+        <v>8812188</v>
       </c>
       <c r="D5" t="n">
-        <v>86611472.56999999</v>
+        <v>7676956.16</v>
       </c>
       <c r="E5" t="n">
-        <v>8760672.800000001</v>
+        <v>2962899.78</v>
       </c>
       <c r="F5" t="n">
-        <v>5000.04</v>
+        <v>4166.7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>988968.42</v>
+        <v>77683.32000000001</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>362722.75</v>
+        <v>83499.82000000001</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>35262532.8</v>
+        <v>458884.8</v>
       </c>
       <c r="C6" t="n">
-        <v>63318024</v>
+        <v>2020788</v>
       </c>
       <c r="D6" t="n">
-        <v>51633647.52</v>
+        <v>1647882.37</v>
       </c>
       <c r="E6" t="n">
-        <v>2353923.94</v>
+        <v>336274.85</v>
       </c>
       <c r="F6" t="n">
-        <v>8333.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>26473.5</v>
+        <v>388.5</v>
       </c>
       <c r="H6" t="n">
-        <v>146652.16</v>
+        <v>33115</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>234323.44</v>
+        <v>26245.06</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>9673418.699999999</v>
+        <v>156123</v>
       </c>
       <c r="C7" t="n">
-        <v>17990280</v>
+        <v>332640</v>
       </c>
       <c r="D7" t="n">
-        <v>16614933.37</v>
+        <v>307209.86</v>
       </c>
       <c r="E7" t="n">
-        <v>529035.95</v>
+        <v>70538.13</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>20895.75</v>
+        <v>166.5</v>
       </c>
       <c r="H7" t="n">
-        <v>42410.44</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>176003.28</v>
+        <v>2712.96</v>
       </c>
     </row>
     <row r="8">
@@ -15587,22 +15581,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2147310</v>
+        <v>3564</v>
       </c>
       <c r="C8" t="n">
-        <v>4241160</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4518585.18</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>81349.33</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11904.75</v>
+        <v>360.75</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15617,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>59391.22</v>
+        <v>401.29</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>516780</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>748440</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>869986.55</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7076.25</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>29071.06</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="10">
@@ -15663,13 +15657,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>313434</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15678,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6105</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27666.54</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,13 +15695,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>112068</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>110880</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>144215.29</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15716,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4995</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>22890.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>54054</v>
-      </c>
-      <c r="C12" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D12" t="n">
-        <v>37197.43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>10456.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>17820</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14652</v>
-      </c>
-      <c r="C14" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D14" t="n">
-        <v>312025.06</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>68820</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3762</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79129.81</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>396</v>
-      </c>
-      <c r="C16" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D16" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>555</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D19" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D21" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D22" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D24" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4759.47</v>
-      </c>
-      <c r="C4" t="n">
-        <v>798840</v>
-      </c>
-      <c r="D4" t="n">
-        <v>627660</v>
-      </c>
-      <c r="E4" t="n">
-        <v>224100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3090</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>31560</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5573.07</v>
-      </c>
-      <c r="C5" t="n">
-        <v>518616</v>
-      </c>
-      <c r="D5" t="n">
-        <v>407484</v>
-      </c>
-      <c r="E5" t="n">
-        <v>95400</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7350</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>23940</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4847.67</v>
-      </c>
-      <c r="C6" t="n">
-        <v>276192</v>
-      </c>
-      <c r="D6" t="n">
-        <v>217008</v>
-      </c>
-      <c r="E6" t="n">
-        <v>47700</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5040</v>
-      </c>
-      <c r="H6" t="n">
-        <v>120</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>13350</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3530.61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D7" t="n">
-        <v>130680</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18900</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3210</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>12180</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2500.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55944</v>
-      </c>
-      <c r="D8" t="n">
-        <v>43956</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2040</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4710</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1689.03</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21780</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>330</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>884.34</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4356</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.13</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>396.99</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>368.73</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.04</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>239.58</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26.37</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2507.88</v>
-      </c>
-      <c r="C5" t="n">
-        <v>285238.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>134877.2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10522.62</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5027.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3878.14</v>
-      </c>
-      <c r="C6" t="n">
-        <v>248572.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>110023.06</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8061.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>252</v>
-      </c>
-      <c r="H6" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4939.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3354.08</v>
-      </c>
-      <c r="C7" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D7" t="n">
-        <v>83373.84</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4020.03</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>481.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7308</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2500.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55944</v>
-      </c>
-      <c r="D8" t="n">
-        <v>32351.62</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1326</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3344.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1689.03</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17489.34</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>280.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>801.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>884.34</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3789.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.13</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>396.99</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>368.73</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.04</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>239.58</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26.37</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5517339.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>15688134</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13667107.08</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1938687.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>107561.52</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47358.11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>8531899.199999999</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13671504</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11148636.26</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1485213.91</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4662</v>
-      </c>
-      <c r="H6" t="n">
-        <v>18922.86</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>46530.09</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7378974.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9147600</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8448271.210000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>740650.33</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8907.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>68841.36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5502024</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3076920</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3278189.25</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24531</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>31501.42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3715866</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1524600</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1772194.82</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5189.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7553.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1945548</v>
-      </c>
-      <c r="C10" t="n">
-        <v>304920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>384012.33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1159686</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>873378</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>811206</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1080288</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>527076</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>94446</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58014</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>15260.4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1675800</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1316700</v>
-      </c>
-      <c r="E4" t="n">
-        <v>699300</v>
-      </c>
-      <c r="F4" t="n">
-        <v>26</v>
-      </c>
-      <c r="G4" t="n">
-        <v>46620</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3840</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>164520</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2992.05</v>
-      </c>
-      <c r="C5" t="n">
-        <v>291312</v>
-      </c>
-      <c r="D5" t="n">
-        <v>228888</v>
-      </c>
-      <c r="E5" t="n">
-        <v>145800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9060</v>
-      </c>
-      <c r="H5" t="n">
-        <v>780</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>42210</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>260.73</v>
-      </c>
-      <c r="C6" t="n">
-        <v>40824</v>
-      </c>
-      <c r="D6" t="n">
-        <v>32076</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>420</v>
-      </c>
-      <c r="H6" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7530</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6048</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4752</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1346.42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>160221.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>75761.92999999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16081.74</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>280.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8864.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>208.58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>36741.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16262.53</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1825.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2786.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>70.95999999999999</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6048</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3031.78</v>
-      </c>
-      <c r="E7" t="n">
-        <v>382.86</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2962129.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>8812188</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7676956.16</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2962899.78</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>77683.32000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>83499.82000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>458884.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2020788</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1647882.37</v>
-      </c>
-      <c r="E6" t="n">
-        <v>336274.85</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>388.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>26245.06</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>156123</v>
-      </c>
-      <c r="C7" t="n">
-        <v>332640</v>
-      </c>
-      <c r="D7" t="n">
-        <v>307209.86</v>
-      </c>
-      <c r="E7" t="n">
-        <v>70538.13</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2712.96</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3564</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>360.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>401.29</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>686.72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>63720</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>35</v>
@@ -576,7 +576,7 @@
         <v>33240</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -614,7 +614,7 @@
         <v>6090</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -652,7 +652,7 @@
         <v>810</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -1546,7 +1546,7 @@
         <v>3600</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>2052</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>567685.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>12900</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>9930</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -9972,7 +9972,7 @@
         <v>210</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -10828,7 +10828,7 @@
         <v>11966.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>4.8</v>
@@ -10866,7 +10866,7 @@
         <v>3471.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -10904,7 +10904,7 @@
         <v>591.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11760,7 +11760,7 @@
         <v>3574.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -11836,7 +11836,7 @@
         <v>153.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
@@ -12692,7 +12692,7 @@
         <v>988968.42</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>
@@ -12768,7 +12768,7 @@
         <v>42410.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>40833.1</v>
@@ -13586,7 +13586,7 @@
         <v>3840</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -16420,7 +16420,7 @@
         <v>3310504.56</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>279998.4</v>
@@ -16458,7 +16458,7 @@
         <v>960335.14</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>116666</v>
@@ -16496,7 +16496,7 @@
         <v>163583.14</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -17314,7 +17314,7 @@
         <v>5490</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>

--- a/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="L4" t="n">
         <v>1243320</v>
@@ -582,7 +582,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="L5" t="n">
         <v>678810</v>
@@ -620,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="L6" t="n">
         <v>273360</v>
@@ -658,7 +658,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L7" t="n">
         <v>120540</v>
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L8" t="n">
         <v>40710</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>12600</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>9900</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2250</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>870</v>
@@ -1476,7 +1476,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L4" t="n">
         <v>107220</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
         <v>69360</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
         <v>34410</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
         <v>15630</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>4830</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2250</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>3450</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>18.48</v>
       </c>
       <c r="L5" t="n">
         <v>14565.6</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="L6" t="n">
         <v>12731.7</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="L7" t="n">
         <v>9378</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>3429.3</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>1822.5</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>3070.5</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>394252.32</v>
       </c>
       <c r="L5" t="n">
         <v>137207.95</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>249607.8</v>
       </c>
       <c r="L6" t="n">
         <v>119932.61</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>122457.16</v>
       </c>
       <c r="L7" t="n">
         <v>88340.75999999999</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>32304.01</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>17167.95</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L10" t="n">
         <v>28924.11</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
         <v>70050</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>20040</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>3600</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="L5" t="n">
         <v>4208.4</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>1332</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71682.24000000001</v>
       </c>
       <c r="L5" t="n">
         <v>39643.13</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>12547.44</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L4" t="n">
         <v>25140</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>7590</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>840</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="L5" t="n">
         <v>1593.9</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>310.8</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>53761.68</v>
       </c>
       <c r="L5" t="n">
         <v>15014.54</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>2927.74</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>169.56</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="L4" t="n">
         <v>276750</v>
@@ -9902,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="L5" t="n">
         <v>183360</v>
@@ -9940,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L6" t="n">
         <v>67230</v>
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
         <v>31140</v>
@@ -10016,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>8880</v>
@@ -10206,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>480</v>
@@ -10834,7 +10834,7 @@
         <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>227.64</v>
       </c>
       <c r="L5" t="n">
         <v>142550.1</v>
@@ -10872,7 +10872,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>127.4</v>
       </c>
       <c r="L6" t="n">
         <v>101143.2</v>
@@ -10910,7 +10910,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>72324</v>
@@ -10948,7 +10948,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="L8" t="n">
         <v>28904.1</v>
@@ -10986,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>10206</v>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>8811</v>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2250</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>870</v>
@@ -11766,7 +11766,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>76.02</v>
       </c>
       <c r="L5" t="n">
         <v>38505.6</v>
@@ -11804,7 +11804,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>44.85</v>
       </c>
       <c r="L6" t="n">
         <v>24875.1</v>
@@ -11842,7 +11842,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>11.48</v>
       </c>
       <c r="L7" t="n">
         <v>18684</v>
@@ -11880,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="L8" t="n">
         <v>6304.8</v>
@@ -12070,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>480</v>
@@ -12698,7 +12698,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1621810.68</v>
       </c>
       <c r="L5" t="n">
         <v>362722.75</v>
@@ -12736,7 +12736,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>956829.9</v>
       </c>
       <c r="L6" t="n">
         <v>234323.44</v>
@@ -12774,7 +12774,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>244914.32</v>
       </c>
       <c r="L7" t="n">
         <v>176003.28</v>
@@ -12812,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>134404.2</v>
       </c>
       <c r="L8" t="n">
         <v>59391.22</v>
@@ -13002,7 +13002,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L13" t="n">
         <v>4521.6</v>
@@ -13592,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
         <v>164520</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>42210</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="L5" t="n">
         <v>8864.1</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>116483.64</v>
       </c>
       <c r="L5" t="n">
         <v>83499.82000000001</v>
@@ -16426,7 +16426,7 @@
         <v>279998.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4856471.76</v>
       </c>
       <c r="L5" t="n">
         <v>1342821.94</v>
@@ -16464,7 +16464,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2717951.6</v>
       </c>
       <c r="L6" t="n">
         <v>952768.9399999999</v>
@@ -16502,7 +16502,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1399510.4</v>
       </c>
       <c r="L7" t="n">
         <v>681292.08</v>
@@ -16540,7 +16540,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>518416.2</v>
       </c>
       <c r="L8" t="n">
         <v>272276.62</v>
@@ -16578,7 +16578,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>170672</v>
       </c>
       <c r="L9" t="n">
         <v>96140.52</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L10" t="n">
         <v>82999.62</v>
@@ -16692,7 +16692,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L12" t="n">
         <v>21195</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L13" t="n">
         <v>8195.4</v>
@@ -17320,7 +17320,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="L4" t="n">
         <v>247470</v>
@@ -17358,7 +17358,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="L5" t="n">
         <v>197490</v>
@@ -17396,7 +17396,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
         <v>108390</v>
@@ -17434,7 +17434,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
         <v>48840</v>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>17070</v>
@@ -17510,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>3840</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>360</v>
@@ -18290,7 +18290,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>84.84</v>
       </c>
       <c r="L5" t="n">
         <v>41472.9</v>
@@ -18328,7 +18328,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
         <v>40104.3</v>
@@ -18366,7 +18366,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>46.74</v>
       </c>
       <c r="L7" t="n">
         <v>29304</v>
@@ -18404,7 +18404,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="L8" t="n">
         <v>12119.7</v>
@@ -18442,7 +18442,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>3110.4</v>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>360</v>
@@ -19222,7 +19222,7 @@
         <v>87499.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1809976.56</v>
       </c>
       <c r="L5" t="n">
         <v>390674.72</v>
@@ -19260,7 +19260,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1386710</v>
       </c>
       <c r="L6" t="n">
         <v>377782.51</v>
@@ -19298,7 +19298,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>997151.16</v>
       </c>
       <c r="L7" t="n">
         <v>276043.68</v>
@@ -19336,7 +19336,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>307209.6</v>
       </c>
       <c r="L8" t="n">
         <v>114167.57</v>
@@ -19374,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L9" t="n">
         <v>29299.97</v>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L12" t="n">
         <v>3391.2</v>
@@ -20116,7 +20116,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="L4" t="n">
         <v>293130</v>
@@ -20154,7 +20154,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L5" t="n">
         <v>104850</v>
@@ -20192,7 +20192,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>19230</v>
@@ -21086,7 +21086,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>35.28</v>
       </c>
       <c r="L5" t="n">
         <v>22018.5</v>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>7115.1</v>
@@ -22018,7 +22018,7 @@
         <v>69999.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>752663.52</v>
       </c>
       <c r="L5" t="n">
         <v>207414.27</v>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>83202.60000000001</v>
       </c>
       <c r="L6" t="n">
         <v>67024.24000000001</v>

--- a/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>153434.88</v>
+        <v>153346.05</v>
       </c>
       <c r="C4" t="n">
         <v>26523000</v>
@@ -532,7 +537,7 @@
         <v>118</v>
       </c>
       <c r="G4" t="n">
-        <v>474180</v>
+        <v>471540</v>
       </c>
       <c r="H4" t="n">
         <v>63720</v>
@@ -544,10 +549,13 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="L4" t="n">
-        <v>1243320</v>
+        <v>1240260</v>
+      </c>
+      <c r="M4" t="n">
+        <v>55530</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>104863.14</v>
+        <v>104830.65</v>
       </c>
       <c r="C5" t="n">
         <v>12294072</v>
@@ -570,7 +578,7 @@
         <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>297510</v>
+        <v>296670</v>
       </c>
       <c r="H5" t="n">
         <v>33240</v>
@@ -582,10 +590,13 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="L5" t="n">
-        <v>678810</v>
+        <v>676920</v>
+      </c>
+      <c r="M5" t="n">
+        <v>29640</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>57239.46</v>
+        <v>57238.2</v>
       </c>
       <c r="C6" t="n">
         <v>4517352</v>
@@ -608,7 +619,7 @@
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>111840</v>
+        <v>111300</v>
       </c>
       <c r="H6" t="n">
         <v>6090</v>
@@ -620,10 +631,13 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L6" t="n">
-        <v>273360</v>
+        <v>272640</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12060</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>27582.66</v>
+        <v>27582.21</v>
       </c>
       <c r="C7" t="n">
         <v>1646568</v>
@@ -646,7 +660,7 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>42720</v>
+        <v>42390</v>
       </c>
       <c r="H7" t="n">
         <v>810</v>
@@ -661,7 +675,10 @@
         <v>80</v>
       </c>
       <c r="L7" t="n">
-        <v>120540</v>
+        <v>119610</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8130</v>
       </c>
     </row>
     <row r="8">
@@ -684,7 +701,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>25500</v>
+        <v>25290</v>
       </c>
       <c r="H8" t="n">
         <v>30</v>
@@ -699,7 +716,10 @@
         <v>27</v>
       </c>
       <c r="L8" t="n">
-        <v>40710</v>
+        <v>40080</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4650</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>7860</v>
+        <v>7680</v>
       </c>
       <c r="H9" t="n">
         <v>120</v>
@@ -737,7 +757,10 @@
         <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>12600</v>
+        <v>12390</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="10">
@@ -775,7 +798,10 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>9900</v>
+        <v>9870</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3120</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4350</v>
+        <v>4320</v>
+      </c>
+      <c r="M11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>2250</v>
+        <v>2220</v>
+      </c>
+      <c r="M12" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>870</v>
       </c>
+      <c r="M13" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>1080</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>30</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>37920</v>
+        <v>37950</v>
       </c>
       <c r="H4" t="n">
         <v>3840</v>
@@ -1479,7 +1556,10 @@
         <v>54</v>
       </c>
       <c r="L4" t="n">
-        <v>107220</v>
+        <v>107400</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9690</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>6881.04</v>
+        <v>6880.95</v>
       </c>
       <c r="C5" t="n">
         <v>656208</v>
@@ -1502,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>30840</v>
+        <v>30870</v>
       </c>
       <c r="H5" t="n">
         <v>2310</v>
@@ -1517,7 +1597,10 @@
         <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>69360</v>
+        <v>69450</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8880</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1623,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>13830</v>
+        <v>13860</v>
       </c>
       <c r="H6" t="n">
         <v>3600</v>
@@ -1555,7 +1638,10 @@
         <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>34410</v>
+        <v>34440</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="7">
@@ -1593,7 +1679,10 @@
         <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>15630</v>
+        <v>15660</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1980</v>
       </c>
     </row>
     <row r="8">
@@ -1633,6 +1722,9 @@
       <c r="L8" t="n">
         <v>4830</v>
       </c>
+      <c r="M8" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1671,6 +1763,9 @@
       <c r="L9" t="n">
         <v>2250</v>
       </c>
+      <c r="M9" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1804,9 @@
       <c r="L10" t="n">
         <v>3450</v>
       </c>
+      <c r="M10" t="n">
+        <v>2430</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,7 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>720</v>
+        <v>750</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1785,6 +1886,9 @@
       <c r="L12" t="n">
         <v>690</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3096.47</v>
+        <v>3096.43</v>
       </c>
       <c r="C5" t="n">
         <v>360914.4</v>
@@ -2446,10 +2598,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>18.48</v>
+        <v>14.56</v>
       </c>
       <c r="L5" t="n">
-        <v>14565.6</v>
+        <v>14584.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>177.6</v>
       </c>
     </row>
     <row r="6">
@@ -2472,22 +2627,25 @@
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>691.5</v>
+        <v>693</v>
       </c>
       <c r="H6" t="n">
         <v>2052</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>11.7</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>12731.7</v>
+        <v>12742.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>280.8</v>
       </c>
     </row>
     <row r="7">
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.74</v>
+        <v>4.47</v>
       </c>
       <c r="L7" t="n">
-        <v>9378</v>
+        <v>9396</v>
+      </c>
+      <c r="M7" t="n">
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -2560,10 +2721,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>3429.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>504</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>1822.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="10">
@@ -2636,10 +2803,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
         <v>3070.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2430</v>
       </c>
     </row>
     <row r="11">
@@ -2677,7 +2847,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>720</v>
+        <v>750</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2717,6 +2890,9 @@
       <c r="L12" t="n">
         <v>690</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2755,6 +2931,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>6812229.6</v>
+        <v>6812140.5</v>
       </c>
       <c r="C5" t="n">
-        <v>19850292</v>
+        <v>15158404.8</v>
       </c>
       <c r="D5" t="n">
-        <v>17293074.27</v>
+        <v>32766902.78</v>
       </c>
       <c r="E5" t="n">
-        <v>4096849.08</v>
+        <v>7671585.6</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -3369,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>230062.14</v>
+        <v>4740120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3378,10 +3602,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>394252.32</v>
+        <v>707169.58</v>
       </c>
       <c r="L5" t="n">
-        <v>137207.95</v>
+        <v>2625210</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53280</v>
       </c>
     </row>
     <row r="6">
@@ -3392,34 +3619,37 @@
         <v>9385675.199999999</v>
       </c>
       <c r="C6" t="n">
-        <v>18735948</v>
+        <v>14307451.2</v>
       </c>
       <c r="D6" t="n">
-        <v>15278514.3</v>
+        <v>28949716.22</v>
       </c>
       <c r="E6" t="n">
-        <v>2746244.59</v>
+        <v>5142501</v>
       </c>
       <c r="F6" t="n">
         <v>12500.1</v>
       </c>
       <c r="G6" t="n">
-        <v>12792.75</v>
+        <v>37422</v>
       </c>
       <c r="H6" t="n">
-        <v>567685.8</v>
+        <v>11696400</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>249607.8</v>
+        <v>443122.06</v>
       </c>
       <c r="L6" t="n">
-        <v>119932.61</v>
+        <v>2293704</v>
+      </c>
+      <c r="M6" t="n">
+        <v>84240</v>
       </c>
     </row>
     <row r="7">
@@ -3430,22 +3660,22 @@
         <v>9166301.1</v>
       </c>
       <c r="C7" t="n">
-        <v>10367280</v>
+        <v>7916832</v>
       </c>
       <c r="D7" t="n">
-        <v>9574707.369999999</v>
+        <v>18142147.58</v>
       </c>
       <c r="E7" t="n">
-        <v>1728184.1</v>
+        <v>3236124.15</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>18315</v>
+        <v>53460</v>
       </c>
       <c r="H7" t="n">
-        <v>36351.81</v>
+        <v>748980</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>122457.16</v>
+        <v>216851.1</v>
       </c>
       <c r="L7" t="n">
-        <v>88340.75999999999</v>
+        <v>1691280</v>
+      </c>
+      <c r="M7" t="n">
+        <v>207900</v>
       </c>
     </row>
     <row r="8">
@@ -3468,19 +3701,19 @@
         <v>5160474</v>
       </c>
       <c r="C8" t="n">
-        <v>3742200</v>
+        <v>2857680</v>
       </c>
       <c r="D8" t="n">
-        <v>3986986.92</v>
+        <v>7554539.52</v>
       </c>
       <c r="E8" t="n">
-        <v>366071.98</v>
+        <v>685490.85</v>
       </c>
       <c r="F8" t="n">
         <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>65656.5</v>
+        <v>191646</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -3492,10 +3725,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57601.8</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>32304.01</v>
+        <v>617274</v>
+      </c>
+      <c r="M8" t="n">
+        <v>151200</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>2403126</v>
       </c>
       <c r="C9" t="n">
-        <v>1136520</v>
+        <v>867888</v>
       </c>
       <c r="D9" t="n">
-        <v>1321090.69</v>
+        <v>2503201.54</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>16511.25</v>
+        <v>48195</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42668</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>17167.95</v>
+        <v>328050</v>
+      </c>
+      <c r="M9" t="n">
+        <v>252000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>1021284</v>
       </c>
       <c r="C10" t="n">
-        <v>1247400</v>
+        <v>952560</v>
       </c>
       <c r="D10" t="n">
-        <v>1570959.52</v>
+        <v>2976652.8</v>
       </c>
       <c r="E10" t="n">
-        <v>144259.92</v>
+        <v>270135</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H10" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3568,10 +3807,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>21334</v>
+        <v>42243.72</v>
       </c>
       <c r="L10" t="n">
-        <v>28924.11</v>
+        <v>552690</v>
+      </c>
+      <c r="M10" t="n">
+        <v>729000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,10 +3824,10 @@
         <v>654984</v>
       </c>
       <c r="C11" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D11" t="n">
-        <v>612914.97</v>
+        <v>1161350.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3594,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3609,7 +3851,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6782.4</v>
+        <v>135000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3620,10 +3865,10 @@
         <v>554004</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3632,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3647,7 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6499.8</v>
+        <v>124200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3658,10 +3906,10 @@
         <v>635382</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3673,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3685,7 +3933,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>702306</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>295612.42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3723,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3734,10 +3988,10 @@
         <v>275418</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3761,6 +4015,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3772,10 +4029,10 @@
         <v>212058</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,6 +4056,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3839,6 +4099,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>21720</v>
+        <v>21750</v>
       </c>
       <c r="H4" t="n">
         <v>1710</v>
@@ -4275,7 +4568,10 @@
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>70050</v>
+        <v>70500</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4313,7 +4609,10 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>20040</v>
+        <v>20100</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>3600</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>870</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>60</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.36</v>
+        <v>2.65</v>
       </c>
       <c r="L5" t="n">
-        <v>4208.4</v>
+        <v>4221</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>1332</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>522</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>42.6</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>1280812.5</v>
       </c>
       <c r="C5" t="n">
-        <v>6479550</v>
+        <v>4948020</v>
       </c>
       <c r="D5" t="n">
-        <v>5644820.71</v>
+        <v>10695801.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1627765.93</v>
+        <v>3048085.35</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17926.92</v>
+        <v>369360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>71682.24000000001</v>
+        <v>128576.29</v>
       </c>
       <c r="L5" t="n">
-        <v>39643.13</v>
+        <v>759780</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>115948.8</v>
       </c>
       <c r="C6" t="n">
-        <v>2095632</v>
+        <v>1600300.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1708915.05</v>
+        <v>3238050.82</v>
       </c>
       <c r="E6" t="n">
-        <v>476389.37</v>
+        <v>892066.5</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1054.5</v>
+        <v>3078</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>12547.44</v>
+        <v>239760</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>40817.7</v>
       </c>
       <c r="C7" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D7" t="n">
-        <v>204806.57</v>
+        <v>388067.33</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>66043.35000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4917.24</v>
+        <v>93960</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>401.29</v>
+        <v>7668</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6331,6 +6783,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>21900</v>
+        <v>21960</v>
       </c>
       <c r="H4" t="n">
         <v>3480</v>
@@ -7071,7 +7580,10 @@
         <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>25140</v>
+        <v>25170</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>7590</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>840</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>30</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.52</v>
+        <v>1.99</v>
       </c>
       <c r="L5" t="n">
         <v>1593.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>310.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>1007899.2</v>
       </c>
       <c r="C5" t="n">
-        <v>3323628</v>
+        <v>2538043.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2895460.98</v>
+        <v>5486317.06</v>
       </c>
       <c r="E5" t="n">
-        <v>91447.52</v>
+        <v>171240.75</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>155366.64</v>
+        <v>3201120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>53761.68</v>
+        <v>96432.22</v>
       </c>
       <c r="L5" t="n">
-        <v>15014.54</v>
+        <v>286902</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>352440</v>
       </c>
       <c r="C6" t="n">
-        <v>1297296</v>
+        <v>990662.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1057899.79</v>
+        <v>2004507.65</v>
       </c>
       <c r="E6" t="n">
-        <v>112091.62</v>
+        <v>209898</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1498.5</v>
+        <v>4374</v>
       </c>
       <c r="H6" t="n">
-        <v>9461.43</v>
+        <v>194940</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>2927.74</v>
+        <v>55944</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,10 +9684,10 @@
         <v>54925.2</v>
       </c>
       <c r="C7" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D7" t="n">
-        <v>51201.64</v>
+        <v>97016.83</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -9034,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>915.75</v>
+        <v>2673</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34987.76</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>169.56</v>
+        <v>3240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>8514</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>115410</v>
+        <v>115470</v>
       </c>
       <c r="H4" t="n">
-        <v>12900</v>
+        <v>12780</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -9867,7 +10592,10 @@
         <v>278</v>
       </c>
       <c r="L4" t="n">
-        <v>276750</v>
+        <v>276810</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16860</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>85050</v>
+        <v>85110</v>
       </c>
       <c r="H5" t="n">
         <v>9930</v>
@@ -9902,10 +10630,13 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L5" t="n">
-        <v>183360</v>
+        <v>183510</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9540</v>
       </c>
     </row>
     <row r="6">
@@ -9928,7 +10659,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>28620</v>
+        <v>28710</v>
       </c>
       <c r="H6" t="n">
         <v>930</v>
@@ -9943,7 +10674,10 @@
         <v>69</v>
       </c>
       <c r="L6" t="n">
-        <v>67230</v>
+        <v>67260</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="7">
@@ -9983,6 +10717,9 @@
       <c r="L7" t="n">
         <v>31140</v>
       </c>
+      <c r="M7" t="n">
+        <v>2460</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>8880</v>
       </c>
+      <c r="M8" t="n">
+        <v>690</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>3810</v>
       </c>
+      <c r="M9" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>3300</v>
       </c>
+      <c r="M10" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>2430</v>
       </c>
+      <c r="M11" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>1110</v>
       </c>
+      <c r="M12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>480</v>
       </c>
+      <c r="M13" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>480</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>47188.41</v>
+        <v>47173.79</v>
       </c>
       <c r="C5" t="n">
         <v>6761739.6</v>
@@ -10828,16 +11628,19 @@
         <v>11966.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>227.64</v>
+        <v>176.75</v>
       </c>
       <c r="L5" t="n">
-        <v>142550.1</v>
+        <v>142153.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>592.8</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>45791.57</v>
+        <v>45790.56</v>
       </c>
       <c r="C6" t="n">
         <v>4065616.8</v>
@@ -10860,22 +11663,25 @@
         <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5592</v>
+        <v>5565</v>
       </c>
       <c r="H6" t="n">
         <v>3471.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>127.4</v>
+        <v>98.86</v>
       </c>
       <c r="L6" t="n">
-        <v>101143.2</v>
+        <v>100876.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>964.8</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>26203.53</v>
+        <v>26203.1</v>
       </c>
       <c r="C7" t="n">
         <v>1646568</v>
@@ -10898,22 +11704,25 @@
         <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6408</v>
+        <v>6358.5</v>
       </c>
       <c r="H7" t="n">
         <v>591.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>65.59999999999999</v>
+        <v>51.04</v>
       </c>
       <c r="L7" t="n">
-        <v>72324</v>
+        <v>71766</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2845.5</v>
       </c>
     </row>
     <row r="8">
@@ -10936,7 +11745,7 @@
         <v>3.8</v>
       </c>
       <c r="G8" t="n">
-        <v>16575</v>
+        <v>16438.5</v>
       </c>
       <c r="H8" t="n">
         <v>25.5</v>
@@ -10948,10 +11757,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>24.3</v>
+        <v>19.87</v>
       </c>
       <c r="L8" t="n">
-        <v>28904.1</v>
+        <v>28456.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2790</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6681</v>
+        <v>6528</v>
       </c>
       <c r="H9" t="n">
         <v>120</v>
@@ -10986,10 +11798,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>6.42</v>
       </c>
       <c r="L9" t="n">
-        <v>10206</v>
+        <v>10035.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="10">
@@ -11024,10 +11839,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
-        <v>8811</v>
+        <v>8784.299999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3120</v>
       </c>
     </row>
     <row r="11">
@@ -11065,7 +11883,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4350</v>
+        <v>4320</v>
+      </c>
+      <c r="M11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="L12" t="n">
-        <v>2250</v>
+        <v>2220</v>
+      </c>
+      <c r="M12" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="13">
@@ -11138,9 +11962,12 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
+        <v>870</v>
+      </c>
+      <c r="M13" t="n">
         <v>870</v>
       </c>
     </row>
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>1080</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11219,6 +12049,9 @@
       <c r="L15" t="n">
         <v>30</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>3574.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>76.02</v>
+        <v>60.24</v>
       </c>
       <c r="L5" t="n">
-        <v>38505.6</v>
+        <v>38537.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>190.8</v>
       </c>
     </row>
     <row r="6">
@@ -11792,7 +12667,7 @@
         <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1431</v>
+        <v>1435.5</v>
       </c>
       <c r="H6" t="n">
         <v>530.1</v>
@@ -11804,10 +12679,13 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>44.85</v>
+        <v>34.98</v>
       </c>
       <c r="L6" t="n">
-        <v>24875.1</v>
+        <v>24886.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>268.8</v>
       </c>
     </row>
     <row r="7">
@@ -11836,16 +12714,19 @@
         <v>153.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>11.48</v>
+        <v>8.93</v>
       </c>
       <c r="L7" t="n">
         <v>18684</v>
+      </c>
+      <c r="M7" t="n">
+        <v>861</v>
       </c>
     </row>
     <row r="8">
@@ -11880,10 +12761,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.3</v>
+        <v>5.15</v>
       </c>
       <c r="L8" t="n">
         <v>6304.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -11923,6 +12807,9 @@
       <c r="L9" t="n">
         <v>3086.1</v>
       </c>
+      <c r="M9" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>2937</v>
       </c>
+      <c r="M10" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>2430</v>
       </c>
+      <c r="M11" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>1110</v>
       </c>
+      <c r="M12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12070,10 +12966,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>480</v>
+      </c>
+      <c r="M13" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="14">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>480</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>36998151.3</v>
       </c>
       <c r="C5" t="n">
-        <v>99419166</v>
+        <v>75920090.40000001</v>
       </c>
       <c r="D5" t="n">
-        <v>86611472.56999999</v>
+        <v>164111346.43</v>
       </c>
       <c r="E5" t="n">
-        <v>8760672.800000001</v>
+        <v>16404863.85</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>988968.42</v>
+        <v>20376360</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1621810.68</v>
+        <v>2925110.55</v>
       </c>
       <c r="L5" t="n">
-        <v>362722.75</v>
+        <v>6936678</v>
+      </c>
+      <c r="M5" t="n">
+        <v>57240</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>35262532.8</v>
       </c>
       <c r="C6" t="n">
-        <v>63318024</v>
+        <v>48351945.6</v>
       </c>
       <c r="D6" t="n">
-        <v>51633647.52</v>
+        <v>97835392.51000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2353923.94</v>
+        <v>4407858</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>26473.5</v>
+        <v>77517</v>
       </c>
       <c r="H6" t="n">
-        <v>146652.16</v>
+        <v>3021570</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>956829.9</v>
+        <v>1698634.55</v>
       </c>
       <c r="L6" t="n">
-        <v>234323.44</v>
+        <v>4479516</v>
+      </c>
+      <c r="M6" t="n">
+        <v>80640</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>9673418.699999999</v>
       </c>
       <c r="C7" t="n">
-        <v>17990280</v>
+        <v>13738032</v>
       </c>
       <c r="D7" t="n">
-        <v>16614933.37</v>
+        <v>31481961.98</v>
       </c>
       <c r="E7" t="n">
-        <v>529035.95</v>
+        <v>990650.25</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>20895.75</v>
+        <v>60993</v>
       </c>
       <c r="H7" t="n">
-        <v>42410.44</v>
+        <v>873810</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>244914.32</v>
+        <v>433702.19</v>
       </c>
       <c r="L7" t="n">
-        <v>176003.28</v>
+        <v>3363120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>258300</v>
       </c>
     </row>
     <row r="8">
@@ -12788,19 +13741,19 @@
         <v>2147310</v>
       </c>
       <c r="C8" t="n">
-        <v>4241160</v>
+        <v>3238704</v>
       </c>
       <c r="D8" t="n">
-        <v>4518585.18</v>
+        <v>8561811.460000001</v>
       </c>
       <c r="E8" t="n">
-        <v>81349.33</v>
+        <v>152331.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11904.75</v>
+        <v>34749</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12812,10 +13765,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>134404.2</v>
+        <v>250160.51</v>
       </c>
       <c r="L8" t="n">
-        <v>59391.22</v>
+        <v>1134864</v>
+      </c>
+      <c r="M8" t="n">
+        <v>124200</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>516780</v>
       </c>
       <c r="C9" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D9" t="n">
-        <v>869986.55</v>
+        <v>1648449.79</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7076.25</v>
+        <v>20655</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12853,7 +13809,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>29071.06</v>
+        <v>555498</v>
+      </c>
+      <c r="M9" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,10 +13823,10 @@
         <v>313434</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>264591.36</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12876,10 +13835,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6105</v>
+        <v>17820</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27666.54</v>
+        <v>528660</v>
+      </c>
+      <c r="M10" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>112068</v>
       </c>
       <c r="C11" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D11" t="n">
-        <v>144215.29</v>
+        <v>273259.01</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>22890.6</v>
+        <v>437400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,10 +13905,10 @@
         <v>54054</v>
       </c>
       <c r="C12" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D12" t="n">
-        <v>37197.43</v>
+        <v>70481.66</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12952,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10456.2</v>
+        <v>199800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>17820</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13002,10 +13970,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21334</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>4521.6</v>
+        <v>86400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,10 +13987,10 @@
         <v>14652</v>
       </c>
       <c r="C14" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D14" t="n">
-        <v>312025.06</v>
+        <v>591224.83</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13028,7 +13999,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>68820</v>
+        <v>200880</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4521.6</v>
+        <v>86400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>3762</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,6 +14055,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13092,10 +14069,10 @@
         <v>396</v>
       </c>
       <c r="C16" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D16" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,6 +14096,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13130,10 +14110,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13157,6 +14137,9 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13197,6 +14180,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13282,10 +14274,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13309,6 +14301,9 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D22" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D24" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>46620</v>
+        <v>46710</v>
       </c>
       <c r="H4" t="n">
         <v>3840</v>
@@ -13595,7 +14608,10 @@
         <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>164520</v>
+        <v>166350</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13633,7 +14649,10 @@
         <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>42210</v>
+        <v>41790</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="H6" t="n">
         <v>210</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7530</v>
+        <v>7950</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>480</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>60</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>90</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.46</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>8864.1</v>
+        <v>8775.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>25.5</v>
       </c>
       <c r="H6" t="n">
         <v>119.7</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2786.1</v>
+        <v>2941.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>288</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>42.6</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>2962129.5</v>
       </c>
       <c r="C5" t="n">
-        <v>8812188</v>
+        <v>6729307.2</v>
       </c>
       <c r="D5" t="n">
-        <v>7676956.16</v>
+        <v>14546290.18</v>
       </c>
       <c r="E5" t="n">
-        <v>2962899.78</v>
+        <v>5548200.3</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>77683.32000000001</v>
+        <v>1600560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>116483.64</v>
+        <v>208936.47</v>
       </c>
       <c r="L5" t="n">
-        <v>83499.82000000001</v>
+        <v>1579662</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>458884.8</v>
       </c>
       <c r="C6" t="n">
-        <v>2020788</v>
+        <v>1543147.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1647882.37</v>
+        <v>3122406.14</v>
       </c>
       <c r="E6" t="n">
-        <v>336274.85</v>
+        <v>629694</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>388.5</v>
+        <v>1377</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>682290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>26245.06</v>
+        <v>529470</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>156123</v>
       </c>
       <c r="C7" t="n">
-        <v>332640</v>
+        <v>254016</v>
       </c>
       <c r="D7" t="n">
-        <v>307209.86</v>
+        <v>582100.99</v>
       </c>
       <c r="E7" t="n">
-        <v>70538.13</v>
+        <v>132086.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2712.96</v>
+        <v>51840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>401.29</v>
+        <v>7668</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>686.72</v>
+        <v>13122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>103814508.6</v>
+        <v>103782343.5</v>
       </c>
       <c r="C5" t="n">
-        <v>371895678</v>
+        <v>283993063.2</v>
       </c>
       <c r="D5" t="n">
-        <v>323986144.83</v>
+        <v>613888678.66</v>
       </c>
       <c r="E5" t="n">
-        <v>45888367.54</v>
+        <v>85928608.34999999</v>
       </c>
       <c r="F5" t="n">
         <v>45000.36</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3310504.56</v>
+        <v>68208480</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>279998.4</v>
+        <v>116534.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4856471.76</v>
+        <v>8582467.220000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1342821.94</v>
+        <v>25587576</v>
+      </c>
+      <c r="M5" t="n">
+        <v>177840</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>100741449.6</v>
+        <v>100739232</v>
       </c>
       <c r="C6" t="n">
-        <v>223608924</v>
+        <v>170755905.6</v>
       </c>
       <c r="D6" t="n">
-        <v>182345304.45</v>
+        <v>345507731.71</v>
       </c>
       <c r="E6" t="n">
-        <v>24015628.73</v>
+        <v>44970646.5</v>
       </c>
       <c r="F6" t="n">
         <v>154167.9</v>
       </c>
       <c r="G6" t="n">
-        <v>103452</v>
+        <v>300510</v>
       </c>
       <c r="H6" t="n">
-        <v>960335.14</v>
+        <v>19786410</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2717951.6</v>
+        <v>4800488.94</v>
       </c>
       <c r="L6" t="n">
-        <v>952768.9399999999</v>
+        <v>18157824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>289440</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>57647759.4</v>
+        <v>57646818.9</v>
       </c>
       <c r="C7" t="n">
-        <v>90561240</v>
+        <v>69155856</v>
       </c>
       <c r="D7" t="n">
-        <v>83637884.95</v>
+        <v>158476995.07</v>
       </c>
       <c r="E7" t="n">
-        <v>11039216.78</v>
+        <v>20671568.55</v>
       </c>
       <c r="F7" t="n">
         <v>175001.4</v>
       </c>
       <c r="G7" t="n">
-        <v>118548</v>
+        <v>343359</v>
       </c>
       <c r="H7" t="n">
-        <v>163583.14</v>
+        <v>3370410</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1399510.4</v>
+        <v>2478298.24</v>
       </c>
       <c r="L7" t="n">
-        <v>681292.08</v>
+        <v>12917880</v>
+      </c>
+      <c r="M7" t="n">
+        <v>853650</v>
       </c>
     </row>
     <row r="8">
@@ -16516,34 +17757,37 @@
         <v>31856022</v>
       </c>
       <c r="C8" t="n">
-        <v>27248760</v>
+        <v>20808144</v>
       </c>
       <c r="D8" t="n">
-        <v>29031171.46</v>
+        <v>55008239.62</v>
       </c>
       <c r="E8" t="n">
-        <v>2277781.23</v>
+        <v>4265276.4</v>
       </c>
       <c r="F8" t="n">
         <v>158334.6</v>
       </c>
       <c r="G8" t="n">
-        <v>306637.5</v>
+        <v>887679</v>
       </c>
       <c r="H8" t="n">
-        <v>7054.58</v>
+        <v>145350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>518416.2</v>
+        <v>964904.83</v>
       </c>
       <c r="L8" t="n">
-        <v>272276.62</v>
+        <v>5122224</v>
+      </c>
+      <c r="M8" t="n">
+        <v>837000</v>
       </c>
     </row>
     <row r="9">
@@ -16554,22 +17798,22 @@
         <v>14145318</v>
       </c>
       <c r="C9" t="n">
-        <v>6819120</v>
+        <v>5207328</v>
       </c>
       <c r="D9" t="n">
-        <v>7926544.11</v>
+        <v>15019209.22</v>
       </c>
       <c r="E9" t="n">
-        <v>1065334.64</v>
+        <v>1994900.4</v>
       </c>
       <c r="F9" t="n">
         <v>125001</v>
       </c>
       <c r="G9" t="n">
-        <v>123598.5</v>
+        <v>352512</v>
       </c>
       <c r="H9" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16578,10 +17822,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>170672</v>
+        <v>311923.74</v>
       </c>
       <c r="L9" t="n">
-        <v>96140.52</v>
+        <v>1806462</v>
+      </c>
+      <c r="M9" t="n">
+        <v>630000</v>
       </c>
     </row>
     <row r="10">
@@ -16592,22 +17839,22 @@
         <v>5941980</v>
       </c>
       <c r="C10" t="n">
-        <v>3076920</v>
+        <v>2349648</v>
       </c>
       <c r="D10" t="n">
-        <v>3875033.49</v>
+        <v>7342410.24</v>
       </c>
       <c r="E10" t="n">
-        <v>288519.84</v>
+        <v>540270</v>
       </c>
       <c r="F10" t="n">
         <v>41667</v>
       </c>
       <c r="G10" t="n">
-        <v>34410</v>
+        <v>100440</v>
       </c>
       <c r="H10" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16616,10 +17863,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>21334</v>
+        <v>42243.72</v>
       </c>
       <c r="L10" t="n">
-        <v>82999.62</v>
+        <v>1581174</v>
+      </c>
+      <c r="M10" t="n">
+        <v>936000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,19 +17880,19 @@
         <v>3141666</v>
       </c>
       <c r="C11" t="n">
-        <v>1219680</v>
+        <v>931392</v>
       </c>
       <c r="D11" t="n">
-        <v>1586368.17</v>
+        <v>3005849.09</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>17760</v>
+        <v>51840</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -16657,7 +17907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>40977</v>
+        <v>777600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>2260368</v>
       </c>
       <c r="C12" t="n">
-        <v>609840</v>
+        <v>465696</v>
       </c>
       <c r="D12" t="n">
-        <v>818343.51</v>
+        <v>1550596.61</v>
       </c>
       <c r="E12" t="n">
-        <v>158520.1</v>
+        <v>296838</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>11655</v>
+        <v>34020</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16692,10 +17945,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>21334</v>
+        <v>45011.41</v>
       </c>
       <c r="L12" t="n">
-        <v>21195</v>
+        <v>399600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,10 +17962,10 @@
         <v>2196216</v>
       </c>
       <c r="C13" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D13" t="n">
-        <v>723905.37</v>
+        <v>1371655.3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16718,10 +17974,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>6105</v>
+        <v>17820</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16730,10 +17986,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21334</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>8195.4</v>
+        <v>156600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>261000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,10 +18003,10 @@
         <v>2154438</v>
       </c>
       <c r="C14" t="n">
-        <v>415800</v>
+        <v>317520</v>
       </c>
       <c r="D14" t="n">
-        <v>585046.99</v>
+        <v>1108546.56</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16756,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>77145</v>
+        <v>225180</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10173.6</v>
+        <v>194400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>898326</v>
       </c>
       <c r="C15" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D15" t="n">
-        <v>276954.35</v>
+        <v>524772.86</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16794,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -16809,7 +18071,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>319374</v>
       </c>
       <c r="C16" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D16" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -16848,6 +18113,9 @@
       </c>
       <c r="L16" t="n">
         <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,10 +18126,10 @@
         <v>66330</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16886,6 +18154,9 @@
       </c>
       <c r="L17" t="n">
         <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="18">
@@ -16925,6 +18196,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>45000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16934,10 +18208,10 @@
         <v>396</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16961,6 +18235,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16972,10 +18249,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16999,6 +18276,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17010,10 +18290,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17037,6 +18317,9 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D22" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D24" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>35132.58</v>
+        <v>35053.65</v>
       </c>
       <c r="C4" t="n">
         <v>5050584</v>
@@ -17308,7 +18609,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>100020</v>
+        <v>97230</v>
       </c>
       <c r="H4" t="n">
         <v>5490</v>
@@ -17320,10 +18621,13 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L4" t="n">
-        <v>247470</v>
+        <v>244530</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21960</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>34800.39</v>
+        <v>34777.98</v>
       </c>
       <c r="C5" t="n">
         <v>3589992</v>
@@ -17346,7 +18650,7 @@
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>92970</v>
+        <v>92220</v>
       </c>
       <c r="H5" t="n">
         <v>1320</v>
@@ -17358,10 +18662,13 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L5" t="n">
-        <v>197490</v>
+        <v>195660</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7200</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>21969.54</v>
+        <v>21968.28</v>
       </c>
       <c r="C6" t="n">
         <v>1721160</v>
@@ -17384,7 +18691,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>47220</v>
+        <v>46620</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L6" t="n">
-        <v>108390</v>
+        <v>107700</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2910</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>12412.44</v>
+        <v>12411.99</v>
       </c>
       <c r="C7" t="n">
         <v>740376</v>
@@ -17422,7 +18732,7 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>19230</v>
+        <v>18960</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17437,7 +18747,10 @@
         <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>48840</v>
+        <v>47910</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="8">
@@ -17460,7 +18773,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>15150</v>
+        <v>14940</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -17475,7 +18788,10 @@
         <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>17070</v>
+        <v>16440</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2340</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>5160</v>
+        <v>4980</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17513,7 +18829,10 @@
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>3840</v>
+        <v>3630</v>
+      </c>
+      <c r="M9" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2010</v>
+        <v>1980</v>
+      </c>
+      <c r="M10" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>720</v>
+        <v>690</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>360</v>
+        <v>330</v>
+      </c>
+      <c r="M12" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>150</v>
       </c>
+      <c r="M13" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>60</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>30</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>15660.18</v>
+        <v>15650.09</v>
       </c>
       <c r="C5" t="n">
         <v>1974495.6</v>
@@ -18290,10 +19666,13 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>84.84</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>41472.9</v>
+        <v>41088.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>17575.63</v>
+        <v>17574.62</v>
       </c>
       <c r="C6" t="n">
         <v>1549044</v>
@@ -18316,7 +19695,7 @@
         <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2361</v>
+        <v>2331</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>50.19</v>
       </c>
       <c r="L6" t="n">
-        <v>40104.3</v>
+        <v>39849</v>
+      </c>
+      <c r="M6" t="n">
+        <v>232.8</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>11791.82</v>
+        <v>11791.39</v>
       </c>
       <c r="C7" t="n">
         <v>740376</v>
@@ -18354,7 +19736,7 @@
         <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2884.5</v>
+        <v>2844</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -18366,10 +19748,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>46.74</v>
+        <v>36.37</v>
       </c>
       <c r="L7" t="n">
-        <v>29304</v>
+        <v>28746</v>
+      </c>
+      <c r="M7" t="n">
+        <v>724.5</v>
       </c>
     </row>
     <row r="8">
@@ -18392,7 +19777,7 @@
         <v>0.95</v>
       </c>
       <c r="G8" t="n">
-        <v>9847.5</v>
+        <v>9711</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -18404,10 +19789,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>14.4</v>
+        <v>11.78</v>
       </c>
       <c r="L8" t="n">
-        <v>12119.7</v>
+        <v>11672.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1404</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>4386</v>
+        <v>4233</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.02</v>
       </c>
       <c r="L9" t="n">
-        <v>3110.4</v>
+        <v>2940.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="10">
@@ -18483,7 +19874,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1788.9</v>
+        <v>1762.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -18521,7 +19915,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>720</v>
+        <v>690</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -18556,10 +19953,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="L12" t="n">
-        <v>360</v>
+        <v>330</v>
+      </c>
+      <c r="M12" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>150</v>
       </c>
+      <c r="M13" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>60</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>30</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>34452386.1</v>
+        <v>34430200.2</v>
       </c>
       <c r="C5" t="n">
-        <v>108597258</v>
+        <v>82928815.2</v>
       </c>
       <c r="D5" t="n">
-        <v>94607195.08</v>
+        <v>179261634.82</v>
       </c>
       <c r="E5" t="n">
-        <v>17740819.66</v>
+        <v>33220705.5</v>
       </c>
       <c r="F5" t="n">
         <v>11666.76</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>131464.08</v>
+        <v>2708640</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>1809976.56</v>
+        <v>3117974.98</v>
       </c>
       <c r="L5" t="n">
-        <v>390674.72</v>
+        <v>7395948</v>
+      </c>
+      <c r="M5" t="n">
+        <v>43200</v>
       </c>
     </row>
     <row r="6">
@@ -19233,22 +20684,22 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>38666390.4</v>
+        <v>38664172.8</v>
       </c>
       <c r="C6" t="n">
-        <v>85197420</v>
+        <v>65059848</v>
       </c>
       <c r="D6" t="n">
-        <v>69475534.39</v>
+        <v>131642184.96</v>
       </c>
       <c r="E6" t="n">
-        <v>13731222.96</v>
+        <v>25712505</v>
       </c>
       <c r="F6" t="n">
         <v>95834.10000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>43678.5</v>
+        <v>125874</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -19257,13 +20708,16 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1386710</v>
+        <v>2437171.31</v>
       </c>
       <c r="L6" t="n">
-        <v>377782.51</v>
+        <v>7172820</v>
+      </c>
+      <c r="M6" t="n">
+        <v>69840</v>
       </c>
     </row>
     <row r="7">
@@ -19271,22 +20725,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>25941999.6</v>
+        <v>25941059.1</v>
       </c>
       <c r="C7" t="n">
-        <v>40720680</v>
+        <v>31095792</v>
       </c>
       <c r="D7" t="n">
-        <v>37607607.28</v>
+        <v>71258863.09999999</v>
       </c>
       <c r="E7" t="n">
-        <v>6877467.32</v>
+        <v>12878453.25</v>
       </c>
       <c r="F7" t="n">
         <v>100000.8</v>
       </c>
       <c r="G7" t="n">
-        <v>53363.25</v>
+        <v>153576</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -19295,13 +20749,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>997151.16</v>
+        <v>1765787.5</v>
       </c>
       <c r="L7" t="n">
-        <v>276043.68</v>
+        <v>5174280</v>
+      </c>
+      <c r="M7" t="n">
+        <v>217350</v>
       </c>
     </row>
     <row r="8">
@@ -19312,19 +20769,19 @@
         <v>16152246</v>
       </c>
       <c r="C8" t="n">
-        <v>12501720</v>
+        <v>9546768</v>
       </c>
       <c r="D8" t="n">
-        <v>13319489.65</v>
+        <v>25237757.95</v>
       </c>
       <c r="E8" t="n">
-        <v>1382938.6</v>
+        <v>2589632.1</v>
       </c>
       <c r="F8" t="n">
         <v>39583.65</v>
       </c>
       <c r="G8" t="n">
-        <v>182178.75</v>
+        <v>524394</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19333,13 +20790,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>307209.6</v>
+        <v>571795.46</v>
       </c>
       <c r="L8" t="n">
-        <v>114167.57</v>
+        <v>2101032</v>
+      </c>
+      <c r="M8" t="n">
+        <v>421200</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>6116220</v>
       </c>
       <c r="C9" t="n">
-        <v>2328480</v>
+        <v>1778112</v>
       </c>
       <c r="D9" t="n">
-        <v>2706624.82</v>
+        <v>5128510.46</v>
       </c>
       <c r="E9" t="n">
-        <v>621445.2</v>
+        <v>1163691.9</v>
       </c>
       <c r="F9" t="n">
         <v>83334</v>
       </c>
       <c r="G9" t="n">
-        <v>81141</v>
+        <v>228582</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19374,10 +20834,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>106670</v>
+        <v>194952.34</v>
       </c>
       <c r="L9" t="n">
-        <v>29299.97</v>
+        <v>529254</v>
+      </c>
+      <c r="M9" t="n">
+        <v>234000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,19 +20851,19 @@
         <v>1815660</v>
       </c>
       <c r="C10" t="n">
-        <v>1275120</v>
+        <v>973728</v>
       </c>
       <c r="D10" t="n">
-        <v>1605869.73</v>
+        <v>3042800.64</v>
       </c>
       <c r="E10" t="n">
-        <v>144259.92</v>
+        <v>270135</v>
       </c>
       <c r="F10" t="n">
         <v>41667</v>
       </c>
       <c r="G10" t="n">
-        <v>13875</v>
+        <v>40500</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19415,7 +20878,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>16851.44</v>
+        <v>317196</v>
+      </c>
+      <c r="M10" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,10 +20892,10 @@
         <v>741114</v>
       </c>
       <c r="C11" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D11" t="n">
-        <v>288430.58</v>
+        <v>546518.02</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19438,7 +20904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -19453,7 +20919,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6782.4</v>
+        <v>124200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>433224</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
-        <v>158520.1</v>
+        <v>296838</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19488,10 +20957,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>21334</v>
+        <v>45011.41</v>
       </c>
       <c r="L12" t="n">
-        <v>3391.2</v>
+        <v>59400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,10 +20974,10 @@
         <v>361350</v>
       </c>
       <c r="C13" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D13" t="n">
-        <v>266701.98</v>
+        <v>505346.69</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19514,7 +20986,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19529,7 +21001,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>162000</v>
       </c>
     </row>
     <row r="14">
@@ -19552,7 +21027,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="15">
@@ -19590,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19605,7 +21083,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -19645,6 +21126,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -19683,6 +21167,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>45000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19949,6 +21454,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,7 +21621,7 @@
         <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>105930</v>
+        <v>106110</v>
       </c>
       <c r="H4" t="n">
         <v>28230</v>
@@ -20119,7 +21636,10 @@
         <v>202</v>
       </c>
       <c r="L4" t="n">
-        <v>293130</v>
+        <v>292560</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>47790</v>
+        <v>47940</v>
       </c>
       <c r="H5" t="n">
-        <v>15240</v>
+        <v>15270</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20157,7 +21677,10 @@
         <v>84</v>
       </c>
       <c r="L5" t="n">
-        <v>104850</v>
+        <v>105540</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6630</v>
+        <v>6720</v>
       </c>
       <c r="H6" t="n">
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>19230</v>
+        <v>18930</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20218,7 +21744,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="H7" t="n">
         <v>420</v>
@@ -20233,7 +21759,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4350</v>
+        <v>4320</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20256,7 +21785,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
         <v>30</v>
@@ -20272,6 +21801,9 @@
       </c>
       <c r="L8" t="n">
         <v>780</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20311,6 +21843,9 @@
       <c r="L9" t="n">
         <v>330</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>30</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5486.4</v>
+        <v>5497.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>35.28</v>
+        <v>27.8</v>
       </c>
       <c r="L5" t="n">
-        <v>22018.5</v>
+        <v>22163.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>331.5</v>
+        <v>336</v>
       </c>
       <c r="H6" t="n">
-        <v>581.4</v>
+        <v>598.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.04</v>
       </c>
       <c r="L6" t="n">
-        <v>7115.1</v>
+        <v>7004.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21150,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="H7" t="n">
         <v>306.6</v>
@@ -21165,7 +22763,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2610</v>
+        <v>2592</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21188,7 +22789,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>39</v>
+        <v>58.5</v>
       </c>
       <c r="H8" t="n">
         <v>25.5</v>
@@ -21204,6 +22805,9 @@
       </c>
       <c r="L8" t="n">
         <v>553.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21243,6 +22847,9 @@
       <c r="L9" t="n">
         <v>267.3</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>26.7</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>11156389.2</v>
       </c>
       <c r="C5" t="n">
-        <v>38008278</v>
+        <v>29024503.2</v>
       </c>
       <c r="D5" t="n">
-        <v>33111854.18</v>
+        <v>62740313.86</v>
       </c>
       <c r="E5" t="n">
-        <v>3017768.29</v>
+        <v>5650944.75</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1517812.56</v>
+        <v>31334040</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>69999.60000000001</v>
+        <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>752663.52</v>
+        <v>1350051.02</v>
       </c>
       <c r="L5" t="n">
-        <v>207414.27</v>
+        <v>3989412</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,22 +23699,22 @@
         <v>1646726.4</v>
       </c>
       <c r="C6" t="n">
-        <v>9629928</v>
+        <v>7353763.2</v>
       </c>
       <c r="D6" t="n">
-        <v>7852871.53</v>
+        <v>14879614.46</v>
       </c>
       <c r="E6" t="n">
-        <v>588480.98</v>
+        <v>1101964.5</v>
       </c>
       <c r="F6" t="n">
         <v>12500.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6132.75</v>
+        <v>18144</v>
       </c>
       <c r="H6" t="n">
-        <v>160844.31</v>
+        <v>3411450</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22056,10 +23723,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>83202.60000000001</v>
+        <v>147707.35</v>
       </c>
       <c r="L6" t="n">
-        <v>67024.24000000001</v>
+        <v>1260738</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>315255.6</v>
       </c>
       <c r="C7" t="n">
-        <v>1441440</v>
+        <v>1100736</v>
       </c>
       <c r="D7" t="n">
-        <v>1331242.74</v>
+        <v>2522437.63</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1665</v>
+        <v>4617</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>1747620</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22097,7 +23767,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>24586.2</v>
+        <v>466560</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>72864</v>
       </c>
       <c r="C8" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D8" t="n">
-        <v>147666.18</v>
+        <v>279797.76</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>3159</v>
       </c>
       <c r="H8" t="n">
-        <v>7054.58</v>
+        <v>145350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5216.8</v>
+        <v>99684</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>25542</v>
       </c>
       <c r="C9" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D9" t="n">
-        <v>32221.72</v>
+        <v>61053.7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22161,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2517.97</v>
+        <v>48114</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>251.51</v>
+        <v>4806</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22251,6 +23933,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>908</v>
+        <v>326</v>
       </c>
       <c r="L4" t="n">
         <v>1240260</v>
@@ -590,7 +590,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>534</v>
+        <v>148</v>
       </c>
       <c r="L5" t="n">
         <v>676920</v>
@@ -631,7 +631,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>195</v>
+        <v>48</v>
       </c>
       <c r="L6" t="n">
         <v>272640</v>
@@ -672,7 +672,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>119610</v>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>40080</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>12390</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>9870</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>2220</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>870</v>
@@ -1553,7 +1553,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>107400</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>69450</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>34440</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>15660</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>4830</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2250</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>3450</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>14.56</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>14584.5</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9.130000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>12742.8</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>9396</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>3429.3</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1822.5</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>3070.5</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>707169.58</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
         <v>2625210</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>443122.06</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
         <v>2293704</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>216851.1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1691280</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>617274</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>328050</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>42243.72</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>552690</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
         <v>70500</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>20100</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.65</v>
+        <v>1.32</v>
       </c>
       <c r="L5" t="n">
         <v>4221</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>128576.29</v>
+        <v>64288.14</v>
       </c>
       <c r="L5" t="n">
         <v>759780</v>
@@ -7577,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>25170</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>7590</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>840</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1593.9</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>310.8</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>96432.22</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>286902</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>55944</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3240</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="L4" t="n">
         <v>276810</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="L5" t="n">
         <v>183510</v>
@@ -10671,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
         <v>67260</v>
@@ -10712,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>31140</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>8880</v>
@@ -10958,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>480</v>
@@ -11634,7 +11634,7 @@
         <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>176.75</v>
+        <v>48.99</v>
       </c>
       <c r="L5" t="n">
         <v>142153.2</v>
@@ -11675,7 +11675,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>98.86</v>
+        <v>24.34</v>
       </c>
       <c r="L6" t="n">
         <v>100876.8</v>
@@ -11716,7 +11716,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>51.04</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>71766</v>
@@ -11757,7 +11757,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>19.87</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>28456.8</v>
@@ -11798,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6.42</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>10035.9</v>
@@ -11839,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>8784.299999999999</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>2220</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>870</v>
@@ -12638,7 +12638,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>60.24</v>
+        <v>18.54</v>
       </c>
       <c r="L5" t="n">
         <v>38537.1</v>
@@ -12679,7 +12679,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>34.98</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>24886.2</v>
@@ -12720,7 +12720,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>8.93</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>18684</v>
@@ -12761,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.15</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>6304.8</v>
@@ -12966,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>480</v>
@@ -13642,7 +13642,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2925110.55</v>
+        <v>900034.02</v>
       </c>
       <c r="L5" t="n">
         <v>6936678</v>
@@ -13683,7 +13683,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1698634.55</v>
+        <v>443122.06</v>
       </c>
       <c r="L6" t="n">
         <v>4479516</v>
@@ -13724,7 +13724,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>433702.19</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
         <v>3363120</v>
@@ -13765,7 +13765,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>250160.51</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
         <v>1134864</v>
@@ -13970,7 +13970,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>46103.92</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>86400</v>
@@ -14605,7 +14605,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="L4" t="n">
         <v>166350</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>41790</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="L5" t="n">
         <v>8775.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>208936.47</v>
+        <v>128576.29</v>
       </c>
       <c r="L5" t="n">
         <v>1579662</v>
@@ -17658,7 +17658,7 @@
         <v>116534.4</v>
       </c>
       <c r="K5" t="n">
-        <v>8582467.220000001</v>
+        <v>2378661.33</v>
       </c>
       <c r="L5" t="n">
         <v>25587576</v>
@@ -17699,7 +17699,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>4800488.94</v>
+        <v>1181658.82</v>
       </c>
       <c r="L6" t="n">
         <v>18157824</v>
@@ -17740,7 +17740,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2478298.24</v>
+        <v>247829.82</v>
       </c>
       <c r="L7" t="n">
         <v>12917880</v>
@@ -17781,7 +17781,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>964904.83</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
         <v>5122224</v>
@@ -17822,7 +17822,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>311923.74</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
         <v>1806462</v>
@@ -17863,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>42243.72</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1581174</v>
@@ -17945,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>45011.41</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>399600</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>46103.92</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>156600</v>
@@ -18621,7 +18621,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="L4" t="n">
         <v>244530</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="L5" t="n">
         <v>195660</v>
@@ -18703,7 +18703,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
         <v>107700</v>
@@ -18744,7 +18744,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>47910</v>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>16440</v>
@@ -18826,7 +18826,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>3630</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>330</v>
@@ -19666,7 +19666,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>64.20999999999999</v>
+        <v>18.21</v>
       </c>
       <c r="L5" t="n">
         <v>41088.6</v>
@@ -19707,7 +19707,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>50.19</v>
+        <v>13.69</v>
       </c>
       <c r="L6" t="n">
         <v>39849</v>
@@ -19748,7 +19748,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>36.37</v>
+        <v>3.19</v>
       </c>
       <c r="L7" t="n">
         <v>28746</v>
@@ -19789,7 +19789,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>11.78</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>11672.4</v>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.02</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
         <v>2940.3</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>330</v>
@@ -20670,7 +20670,7 @@
         <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>3117974.98</v>
+        <v>883961.98</v>
       </c>
       <c r="L5" t="n">
         <v>7395948</v>
@@ -20711,7 +20711,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2437171.31</v>
+        <v>664683.08</v>
       </c>
       <c r="L6" t="n">
         <v>7172820</v>
@@ -20752,7 +20752,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1765787.5</v>
+        <v>154893.64</v>
       </c>
       <c r="L7" t="n">
         <v>5174280</v>
@@ -20793,7 +20793,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>571795.46</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>2101032</v>
@@ -20834,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>194952.34</v>
+        <v>38990.47</v>
       </c>
       <c r="L9" t="n">
         <v>529254</v>
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>45011.41</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>59400</v>
@@ -21633,7 +21633,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
         <v>292560</v>
@@ -21674,7 +21674,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
         <v>105540</v>
@@ -21715,7 +21715,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>18930</v>
@@ -22678,7 +22678,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>27.8</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
         <v>22163.4</v>
@@ -22719,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7004.1</v>
@@ -23682,7 +23682,7 @@
         <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1350051.02</v>
+        <v>257152.58</v>
       </c>
       <c r="L5" t="n">
         <v>3989412</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>147707.35</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1260738</v>

--- a/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Present_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>471540</v>
       </c>
       <c r="H4" t="n">
-        <v>63720</v>
+        <v>71730</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -572,22 +572,22 @@
         <v>326</v>
       </c>
       <c r="L4" t="n">
-        <v>1240260</v>
+        <v>1397160</v>
       </c>
       <c r="M4" t="n">
-        <v>55530</v>
+        <v>66660</v>
       </c>
       <c r="N4" t="n">
-        <v>45420</v>
+        <v>60450</v>
       </c>
       <c r="O4" t="n">
-        <v>252930</v>
+        <v>276000</v>
       </c>
       <c r="P4" t="n">
-        <v>72630</v>
+        <v>32220</v>
       </c>
       <c r="Q4" t="n">
-        <v>190149.1</v>
+        <v>1970496.74</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>296670</v>
       </c>
       <c r="H5" t="n">
-        <v>33240</v>
+        <v>39180</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -625,22 +625,22 @@
         <v>148</v>
       </c>
       <c r="L5" t="n">
-        <v>676920</v>
+        <v>769830</v>
       </c>
       <c r="M5" t="n">
-        <v>29640</v>
+        <v>49560</v>
       </c>
       <c r="N5" t="n">
-        <v>14070</v>
+        <v>17610</v>
       </c>
       <c r="O5" t="n">
-        <v>171120</v>
+        <v>207000</v>
       </c>
       <c r="P5" t="n">
-        <v>85890</v>
+        <v>66300</v>
       </c>
       <c r="Q5" t="n">
-        <v>129990.01</v>
+        <v>1347073.85</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>111300</v>
       </c>
       <c r="H6" t="n">
-        <v>6090</v>
+        <v>8220</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>48</v>
       </c>
       <c r="L6" t="n">
-        <v>272640</v>
+        <v>327750</v>
       </c>
       <c r="M6" t="n">
-        <v>12060</v>
+        <v>32010</v>
       </c>
       <c r="N6" t="n">
-        <v>3720</v>
+        <v>8280</v>
       </c>
       <c r="O6" t="n">
-        <v>64110</v>
+        <v>86700</v>
       </c>
       <c r="P6" t="n">
-        <v>84570</v>
+        <v>66240</v>
       </c>
       <c r="Q6" t="n">
-        <v>70975.37</v>
+        <v>735510.87</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>42390</v>
       </c>
       <c r="H7" t="n">
-        <v>810</v>
+        <v>1440</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -731,22 +731,22 @@
         <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>119610</v>
+        <v>161580</v>
       </c>
       <c r="M7" t="n">
-        <v>8130</v>
+        <v>30840</v>
       </c>
       <c r="N7" t="n">
-        <v>240</v>
+        <v>1050</v>
       </c>
       <c r="O7" t="n">
-        <v>19230</v>
+        <v>37470</v>
       </c>
       <c r="P7" t="n">
-        <v>86850</v>
+        <v>93720</v>
       </c>
       <c r="Q7" t="n">
-        <v>34201.94</v>
+        <v>354431.4</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>25290</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>40080</v>
+        <v>71550</v>
       </c>
       <c r="M8" t="n">
-        <v>4650</v>
+        <v>30960</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>4110</v>
+        <v>10680</v>
       </c>
       <c r="P8" t="n">
-        <v>78150</v>
+        <v>90390</v>
       </c>
       <c r="Q8" t="n">
-        <v>17955.21</v>
+        <v>186068.13</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>7680</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>12390</v>
+        <v>44430</v>
       </c>
       <c r="M9" t="n">
-        <v>2100</v>
+        <v>23220</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>210</v>
+        <v>2220</v>
       </c>
       <c r="P9" t="n">
-        <v>79410</v>
+        <v>125250</v>
       </c>
       <c r="Q9" t="n">
-        <v>7972.82</v>
+        <v>82621.52</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9870</v>
+        <v>38460</v>
       </c>
       <c r="M10" t="n">
-        <v>3120</v>
+        <v>12660</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P10" t="n">
-        <v>52680</v>
+        <v>91350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3349.12</v>
+        <v>34706.57</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>960</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4320</v>
+        <v>27990</v>
       </c>
       <c r="M11" t="n">
-        <v>240</v>
+        <v>4050</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P11" t="n">
-        <v>39000</v>
+        <v>60990</v>
       </c>
       <c r="Q11" t="n">
-        <v>1770.76</v>
+        <v>18350.19</v>
       </c>
     </row>
     <row r="12">
@@ -996,22 +996,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2220</v>
+        <v>14670</v>
       </c>
       <c r="M12" t="n">
-        <v>240</v>
+        <v>5190</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>37170</v>
+        <v>50610</v>
       </c>
       <c r="Q12" t="n">
-        <v>1274.03</v>
+        <v>13202.6</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>330</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>5340</v>
       </c>
       <c r="M13" t="n">
-        <v>870</v>
+        <v>2430</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>33330</v>
+        <v>56070</v>
       </c>
       <c r="Q13" t="n">
-        <v>1237.87</v>
+        <v>12827.9</v>
       </c>
     </row>
     <row r="14">
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1080</v>
+        <v>6390</v>
       </c>
       <c r="M14" t="n">
+        <v>270</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>150</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>60</v>
-      </c>
       <c r="P14" t="n">
-        <v>22530</v>
+        <v>40500</v>
       </c>
       <c r="Q14" t="n">
-        <v>1214.32</v>
+        <v>12583.88</v>
       </c>
     </row>
     <row r="15">
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>2730</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1167,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>7080</v>
+        <v>13560</v>
       </c>
       <c r="Q15" t="n">
-        <v>506.33</v>
+        <v>5247.04</v>
       </c>
     </row>
     <row r="16">
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q16" t="n">
-        <v>180.01</v>
+        <v>1865.43</v>
       </c>
     </row>
     <row r="17">
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37.39</v>
+        <v>387.43</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.71</v>
+        <v>111.02</v>
       </c>
     </row>
     <row r="19">
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1852,7 @@
         <v>37950</v>
       </c>
       <c r="H4" t="n">
-        <v>3840</v>
+        <v>5790</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>107400</v>
+        <v>117690</v>
       </c>
       <c r="M4" t="n">
-        <v>9690</v>
+        <v>6930</v>
       </c>
       <c r="N4" t="n">
-        <v>330</v>
+        <v>1200</v>
       </c>
       <c r="O4" t="n">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2119.28</v>
+        <v>240185.52</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>30870</v>
       </c>
       <c r="H5" t="n">
-        <v>2310</v>
+        <v>2280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>69450</v>
+        <v>82110</v>
       </c>
       <c r="M5" t="n">
-        <v>8880</v>
+        <v>13770</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2064.28</v>
+        <v>233952.3</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>13860</v>
       </c>
       <c r="H6" t="n">
-        <v>3600</v>
+        <v>4140</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1970,22 +1970,22 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>34440</v>
+        <v>45090</v>
       </c>
       <c r="M6" t="n">
-        <v>3510</v>
+        <v>8580</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1599.83</v>
+        <v>181314.18</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>6600</v>
       </c>
       <c r="H7" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15660</v>
+        <v>22380</v>
       </c>
       <c r="M7" t="n">
-        <v>1980</v>
+        <v>5190</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1315.74</v>
+        <v>149116.86</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>5460</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4830</v>
+        <v>10860</v>
       </c>
       <c r="M8" t="n">
-        <v>840</v>
+        <v>3180</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>703.7</v>
+        <v>79752.78</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>1050</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2250</v>
+        <v>3780</v>
       </c>
       <c r="M9" t="n">
-        <v>840</v>
+        <v>1590</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>327.7</v>
+        <v>37139.22</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>180</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3450</v>
+        <v>4890</v>
       </c>
       <c r="M10" t="n">
-        <v>2430</v>
+        <v>3630</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>139.27</v>
+        <v>15783.48</v>
       </c>
     </row>
     <row r="11">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>1560</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>89.31999999999999</v>
+        <v>10122.48</v>
       </c>
     </row>
     <row r="12">
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>690</v>
+        <v>2100</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>75.55</v>
+        <v>8561.879999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,11 +2341,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.64</v>
+        <v>9819.540000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.77</v>
+        <v>10853.82</v>
       </c>
     </row>
     <row r="15">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.56</v>
+        <v>4256.46</v>
       </c>
     </row>
     <row r="16">
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.92</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>831.6</v>
+        <v>820.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>2.98</v>
       </c>
       <c r="L5" t="n">
-        <v>14584.5</v>
+        <v>17243.1</v>
       </c>
       <c r="M5" t="n">
-        <v>177.6</v>
+        <v>275.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>103.21</v>
+        <v>11697.62</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>693</v>
       </c>
       <c r="H6" t="n">
-        <v>2052</v>
+        <v>2359.8</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -3262,22 +3262,22 @@
         <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>12742.8</v>
+        <v>16683.3</v>
       </c>
       <c r="M6" t="n">
-        <v>280.8</v>
+        <v>686.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>67.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1199.87</v>
+        <v>135985.64</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>131.4</v>
+        <v>350.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9396</v>
+        <v>13428</v>
       </c>
       <c r="M7" t="n">
-        <v>693</v>
+        <v>1816.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1052.59</v>
+        <v>119293.49</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>3549</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3429.3</v>
+        <v>7710.6</v>
       </c>
       <c r="M8" t="n">
-        <v>462</v>
+        <v>1749</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>668.52</v>
+        <v>75765.14</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>892.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1822.5</v>
+        <v>3061.8</v>
       </c>
       <c r="M9" t="n">
-        <v>588</v>
+        <v>1113</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>317.87</v>
+        <v>36025.04</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>180</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3070.5</v>
+        <v>4352.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2065.5</v>
+        <v>3085.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>139.27</v>
+        <v>15783.48</v>
       </c>
     </row>
     <row r="11">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>1560</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>89.31999999999999</v>
+        <v>10122.48</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>690</v>
+        <v>2100</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1339.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>75.55</v>
+        <v>8561.879999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,11 +3633,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.64</v>
+        <v>9819.540000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.77</v>
+        <v>10853.82</v>
       </c>
     </row>
     <row r="15">
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.56</v>
+        <v>4256.46</v>
       </c>
     </row>
     <row r="16">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.92</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="17">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4740120</v>
+        <v>4678560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>2625210</v>
+        <v>3103758</v>
       </c>
       <c r="M5" t="n">
-        <v>62160</v>
+        <v>96390</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2550</v>
+        <v>3315</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>61928.55</v>
+        <v>7018569</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>37422</v>
       </c>
       <c r="H6" t="n">
-        <v>11696400</v>
+        <v>13450860</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -4554,22 +4554,22 @@
         <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>2293704</v>
+        <v>3002994</v>
       </c>
       <c r="M6" t="n">
-        <v>98280</v>
+        <v>240240</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7650</v>
+        <v>11475</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>719923.95</v>
+        <v>81591381</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>53460</v>
       </c>
       <c r="H7" t="n">
-        <v>748980</v>
+        <v>1997280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1691280</v>
+        <v>2417040</v>
       </c>
       <c r="M7" t="n">
-        <v>242550</v>
+        <v>635775</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>631553.76</v>
+        <v>71576092.8</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>191646</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>145350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>617274</v>
+        <v>1387908</v>
       </c>
       <c r="M8" t="n">
-        <v>161700</v>
+        <v>612150</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>401109.57</v>
+        <v>45459084.6</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>48195</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>328050</v>
+        <v>551124</v>
       </c>
       <c r="M9" t="n">
-        <v>205800</v>
+        <v>389550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>190720.82</v>
+        <v>21615026.04</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>9720</v>
       </c>
       <c r="H10" t="n">
-        <v>342000</v>
+        <v>1197000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>552690</v>
+        <v>783378</v>
       </c>
       <c r="M10" t="n">
-        <v>722925</v>
+        <v>1079925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>83559.60000000001</v>
+        <v>9470088</v>
       </c>
     </row>
     <row r="11">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>135000</v>
+        <v>280800</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>321300</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53589.6</v>
+        <v>6073488</v>
       </c>
     </row>
     <row r="12">
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>124200</v>
+        <v>378000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>468825</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>45327.6</v>
+        <v>5137128</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16200</v>
+        <v>75600</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>51985.8</v>
+        <v>5891724</v>
       </c>
     </row>
     <row r="14">
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>145800</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57461.4</v>
+        <v>6512292</v>
       </c>
     </row>
     <row r="15">
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>167400</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22534.2</v>
+        <v>2553876</v>
       </c>
     </row>
     <row r="16">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17350.2</v>
+        <v>1966356</v>
       </c>
     </row>
     <row r="17">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>259.2</v>
+        <v>29376</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.8</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="19">
@@ -5728,7 +5728,7 @@
         <v>21750</v>
       </c>
       <c r="H4" t="n">
-        <v>1710</v>
+        <v>2520</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>70500</v>
+        <v>88470</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2370</v>
+        <v>3390</v>
       </c>
       <c r="O4" t="n">
-        <v>16080</v>
+        <v>19230</v>
       </c>
       <c r="P4" t="n">
-        <v>8550</v>
+        <v>8430</v>
       </c>
       <c r="Q4" t="n">
-        <v>12674.59</v>
+        <v>66708.36</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>3840</v>
       </c>
       <c r="H5" t="n">
-        <v>180</v>
+        <v>720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>20100</v>
+        <v>29880</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1020</v>
+        <v>1380</v>
       </c>
       <c r="O5" t="n">
-        <v>2340</v>
+        <v>5220</v>
       </c>
       <c r="P5" t="n">
-        <v>8640</v>
+        <v>13350</v>
       </c>
       <c r="Q5" t="n">
-        <v>2949.75</v>
+        <v>15525</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1140</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3600</v>
+        <v>6480</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5855,13 +5855,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P6" t="n">
-        <v>5880</v>
+        <v>10260</v>
       </c>
       <c r="Q6" t="n">
-        <v>150.21</v>
+        <v>790.5599999999999</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>870</v>
+        <v>2220</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5340</v>
+        <v>11040</v>
       </c>
       <c r="Q7" t="n">
-        <v>44.53</v>
+        <v>234.36</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>60</v>
+        <v>930</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3990</v>
+        <v>9180</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.29</v>
+        <v>143.64</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>840</v>
+        <v>2790</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.54</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="10">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>64.8</v>
+        <v>259.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>1.32</v>
       </c>
       <c r="L5" t="n">
-        <v>4221</v>
+        <v>6274.8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2</v>
+        <v>13.8</v>
       </c>
       <c r="O5" t="n">
-        <v>117</v>
+        <v>261</v>
       </c>
       <c r="P5" t="n">
-        <v>172.8</v>
+        <v>267</v>
       </c>
       <c r="Q5" t="n">
-        <v>147.49</v>
+        <v>776.25</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>57</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>1332</v>
+        <v>2397.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P6" t="n">
-        <v>882</v>
+        <v>1539</v>
       </c>
       <c r="Q6" t="n">
-        <v>112.65</v>
+        <v>592.92</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>522</v>
+        <v>1332</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1335</v>
+        <v>2760</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.62</v>
+        <v>187.49</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>42.6</v>
+        <v>660.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1516.2</v>
+        <v>3488.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.93</v>
+        <v>136.46</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>145.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>420</v>
+        <v>1395</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.37</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="10">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>369360</v>
+        <v>1477440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>64288.14</v>
       </c>
       <c r="L5" t="n">
-        <v>759780</v>
+        <v>1129464</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1734</v>
+        <v>2346</v>
       </c>
       <c r="O5" t="n">
-        <v>19890</v>
+        <v>44370</v>
       </c>
       <c r="P5" t="n">
-        <v>11232</v>
+        <v>17355</v>
       </c>
       <c r="Q5" t="n">
-        <v>88492.5</v>
+        <v>465750</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>3078</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>239760</v>
+        <v>431568</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P6" t="n">
-        <v>57330</v>
+        <v>100035</v>
       </c>
       <c r="Q6" t="n">
-        <v>67592.88</v>
+        <v>355752</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>486</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>93960</v>
+        <v>239760</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>86775</v>
+        <v>179400</v>
       </c>
       <c r="Q7" t="n">
-        <v>21373.63</v>
+        <v>112492.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7668</v>
+        <v>118854</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>98553</v>
+        <v>226746</v>
       </c>
       <c r="Q8" t="n">
-        <v>15556.21</v>
+        <v>81874.8</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>26244</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>27300</v>
+        <v>90675</v>
       </c>
       <c r="Q9" t="n">
-        <v>3224.51</v>
+        <v>16971.12</v>
       </c>
     </row>
     <row r="10">
@@ -9604,7 +9604,7 @@
         <v>21960</v>
       </c>
       <c r="H4" t="n">
-        <v>3480</v>
+        <v>3000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>25170</v>
+        <v>33480</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>13590</v>
+        <v>18570</v>
       </c>
       <c r="O4" t="n">
-        <v>28860</v>
+        <v>27780</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10249.08</v>
+        <v>55615.14</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>4980</v>
       </c>
       <c r="H5" t="n">
-        <v>1560</v>
+        <v>2280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7590</v>
+        <v>9090</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4530</v>
+        <v>3180</v>
       </c>
       <c r="O5" t="n">
-        <v>31500</v>
+        <v>30630</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1313.32</v>
+        <v>7126.56</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>1620</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>840</v>
+        <v>3480</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1770</v>
+        <v>3780</v>
       </c>
       <c r="O6" t="n">
-        <v>14310</v>
+        <v>19470</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>258.32</v>
+        <v>1401.75</v>
       </c>
     </row>
     <row r="7">
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>870</v>
       </c>
       <c r="O7" t="n">
-        <v>2490</v>
+        <v>5220</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>33.9</v>
+        <v>183.96</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>810</v>
+        <v>720</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.99</v>
+        <v>27.09</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.23</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>561.6</v>
+        <v>820.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1593.9</v>
+        <v>1908.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>45.3</v>
+        <v>31.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1575</v>
+        <v>1531.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>65.67</v>
+        <v>356.33</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>81</v>
       </c>
       <c r="H6" t="n">
-        <v>34.2</v>
+        <v>273.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>310.8</v>
+        <v>1287.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>88.5</v>
+        <v>189</v>
       </c>
       <c r="O6" t="n">
-        <v>3577.5</v>
+        <v>4867.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>193.74</v>
+        <v>1051.31</v>
       </c>
     </row>
     <row r="7">
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>60.9</v>
       </c>
       <c r="O7" t="n">
-        <v>871.5</v>
+        <v>1827</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.12</v>
+        <v>147.17</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>364.5</v>
+        <v>324</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.74</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>181.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.23</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3201120</v>
+        <v>4678560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>286902</v>
+        <v>343602</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7701</v>
+        <v>5406</v>
       </c>
       <c r="O5" t="n">
-        <v>267750</v>
+        <v>260355</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>39399.7</v>
+        <v>213796.8</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>4374</v>
       </c>
       <c r="H6" t="n">
-        <v>194940</v>
+        <v>1559520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>55944</v>
+        <v>231768</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>15045</v>
+        <v>32130</v>
       </c>
       <c r="O6" t="n">
-        <v>608175</v>
+        <v>827475</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>116245.12</v>
+        <v>630787.5</v>
       </c>
     </row>
     <row r="7">
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3240</v>
+        <v>16200</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1428</v>
+        <v>10353</v>
       </c>
       <c r="O7" t="n">
-        <v>148155</v>
+        <v>310590</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>16272.58</v>
+        <v>88300.8</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>61965</v>
+        <v>55080</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2845.61</v>
+        <v>15441.3</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>30855</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>135.14</v>
+        <v>733.3200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>115470</v>
       </c>
       <c r="H4" t="n">
-        <v>12780</v>
+        <v>13800</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -13492,19 +13492,19 @@
         <v>136</v>
       </c>
       <c r="L4" t="n">
-        <v>276810</v>
+        <v>270540</v>
       </c>
       <c r="M4" t="n">
-        <v>16860</v>
+        <v>5760</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>52200</v>
+        <v>51300</v>
       </c>
       <c r="P4" t="n">
-        <v>42300</v>
+        <v>13530</v>
       </c>
       <c r="Q4" t="n">
         <v>51074.41</v>
@@ -13533,7 +13533,7 @@
         <v>85110</v>
       </c>
       <c r="H5" t="n">
-        <v>9930</v>
+        <v>10860</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>56</v>
       </c>
       <c r="L5" t="n">
-        <v>183510</v>
+        <v>184620</v>
       </c>
       <c r="M5" t="n">
-        <v>9540</v>
+        <v>7440</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>51390</v>
+        <v>60300</v>
       </c>
       <c r="P5" t="n">
-        <v>41400</v>
+        <v>33390</v>
       </c>
       <c r="Q5" t="n">
         <v>46341.12</v>
@@ -13586,7 +13586,7 @@
         <v>28710</v>
       </c>
       <c r="H6" t="n">
-        <v>930</v>
+        <v>1440</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>67260</v>
+        <v>70680</v>
       </c>
       <c r="M6" t="n">
-        <v>3360</v>
+        <v>9360</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>17040</v>
+        <v>20820</v>
       </c>
       <c r="P6" t="n">
-        <v>37680</v>
+        <v>35640</v>
       </c>
       <c r="Q6" t="n">
         <v>24844.06</v>
@@ -13639,7 +13639,7 @@
         <v>7530</v>
       </c>
       <c r="H7" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -13651,19 +13651,19 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>31140</v>
+        <v>39180</v>
       </c>
       <c r="M7" t="n">
-        <v>2460</v>
+        <v>11730</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>9810</v>
+        <v>12660</v>
       </c>
       <c r="P7" t="n">
-        <v>39510</v>
+        <v>42270</v>
       </c>
       <c r="Q7" t="n">
         <v>5739.25</v>
@@ -13692,7 +13692,7 @@
         <v>990</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>8880</v>
+        <v>20880</v>
       </c>
       <c r="M8" t="n">
-        <v>690</v>
+        <v>16470</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1920</v>
+        <v>3360</v>
       </c>
       <c r="P8" t="n">
-        <v>36630</v>
+        <v>42120</v>
       </c>
       <c r="Q8" t="n">
         <v>1210.3</v>
@@ -13757,19 +13757,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3810</v>
+        <v>24690</v>
       </c>
       <c r="M9" t="n">
-        <v>330</v>
+        <v>11340</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P9" t="n">
-        <v>38250</v>
+        <v>61350</v>
       </c>
       <c r="Q9" t="n">
         <v>291.28</v>
@@ -13810,19 +13810,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3300</v>
+        <v>22980</v>
       </c>
       <c r="M10" t="n">
-        <v>360</v>
+        <v>6570</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
-        <v>26850</v>
+        <v>47970</v>
       </c>
       <c r="Q10" t="n">
         <v>176.66</v>
@@ -13851,7 +13851,7 @@
         <v>270</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13863,10 +13863,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2430</v>
+        <v>20040</v>
       </c>
       <c r="M11" t="n">
-        <v>180</v>
+        <v>2010</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>17700</v>
+        <v>32580</v>
       </c>
       <c r="Q11" t="n">
         <v>63.17</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1110</v>
+        <v>9360</v>
       </c>
       <c r="M12" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14310</v>
+        <v>18510</v>
       </c>
       <c r="Q12" t="n">
         <v>30.47</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>480</v>
+        <v>3930</v>
       </c>
       <c r="M13" t="n">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12360</v>
+        <v>30000</v>
       </c>
       <c r="Q13" t="n">
         <v>10.04</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>3540</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5370</v>
+        <v>12630</v>
       </c>
       <c r="Q14" t="n">
         <v>8.26</v>
@@ -14075,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>750</v>
+        <v>1440</v>
       </c>
       <c r="Q15" t="n">
         <v>2.12</v>
@@ -14128,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q16" t="n">
         <v>0.22</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11966.4</v>
+        <v>14104.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -14837,22 +14837,22 @@
         <v>48.99</v>
       </c>
       <c r="L5" t="n">
-        <v>142153.2</v>
+        <v>161664.3</v>
       </c>
       <c r="M5" t="n">
-        <v>592.8</v>
+        <v>991.2</v>
       </c>
       <c r="N5" t="n">
-        <v>140.7</v>
+        <v>176.1</v>
       </c>
       <c r="O5" t="n">
-        <v>8556</v>
+        <v>10350</v>
       </c>
       <c r="P5" t="n">
-        <v>1717.8</v>
+        <v>1326</v>
       </c>
       <c r="Q5" t="n">
-        <v>6499.5</v>
+        <v>67353.69</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>5565</v>
       </c>
       <c r="H6" t="n">
-        <v>3471.3</v>
+        <v>4685.4</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>24.34</v>
       </c>
       <c r="L6" t="n">
-        <v>100876.8</v>
+        <v>121267.5</v>
       </c>
       <c r="M6" t="n">
-        <v>964.8</v>
+        <v>2560.8</v>
       </c>
       <c r="N6" t="n">
-        <v>186</v>
+        <v>414</v>
       </c>
       <c r="O6" t="n">
-        <v>16027.5</v>
+        <v>21675</v>
       </c>
       <c r="P6" t="n">
-        <v>12685.5</v>
+        <v>9936</v>
       </c>
       <c r="Q6" t="n">
-        <v>53231.53</v>
+        <v>551633.15</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>6358.5</v>
       </c>
       <c r="H7" t="n">
-        <v>591.3</v>
+        <v>1051.2</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -14943,22 +14943,22 @@
         <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>71766</v>
+        <v>96948</v>
       </c>
       <c r="M7" t="n">
-        <v>2845.5</v>
+        <v>10794</v>
       </c>
       <c r="N7" t="n">
-        <v>16.8</v>
+        <v>73.5</v>
       </c>
       <c r="O7" t="n">
-        <v>6730.5</v>
+        <v>13114.5</v>
       </c>
       <c r="P7" t="n">
-        <v>21712.5</v>
+        <v>23430</v>
       </c>
       <c r="Q7" t="n">
-        <v>27361.55</v>
+        <v>283545.12</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>16438.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.5</v>
+        <v>153</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -14996,22 +14996,22 @@
         <v>2.94</v>
       </c>
       <c r="L8" t="n">
-        <v>28456.8</v>
+        <v>50800.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2557.5</v>
+        <v>17028</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>1849.5</v>
+        <v>4806</v>
       </c>
       <c r="P8" t="n">
-        <v>29697</v>
+        <v>34348.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>17057.45</v>
+        <v>176764.72</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>6528</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>10035.9</v>
+        <v>35988.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1470</v>
+        <v>16254</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>115.5</v>
+        <v>1221</v>
       </c>
       <c r="P9" t="n">
-        <v>39705</v>
+        <v>62625</v>
       </c>
       <c r="Q9" t="n">
-        <v>7733.63</v>
+        <v>80142.87</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8784.299999999999</v>
+        <v>34229.4</v>
       </c>
       <c r="M10" t="n">
-        <v>2652</v>
+        <v>10761</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="P10" t="n">
-        <v>44778</v>
+        <v>77647.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3349.12</v>
+        <v>34706.56</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>960</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15155,22 +15155,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4320</v>
+        <v>27990</v>
       </c>
       <c r="M11" t="n">
-        <v>216</v>
+        <v>3645</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>25.5</v>
+        <v>76.5</v>
       </c>
       <c r="P11" t="n">
-        <v>35100</v>
+        <v>54891</v>
       </c>
       <c r="Q11" t="n">
-        <v>1770.76</v>
+        <v>18350.19</v>
       </c>
     </row>
     <row r="12">
@@ -15208,22 +15208,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2220</v>
+        <v>14670</v>
       </c>
       <c r="M12" t="n">
-        <v>228</v>
+        <v>4930.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>37170</v>
+        <v>50610</v>
       </c>
       <c r="Q12" t="n">
-        <v>1274.03</v>
+        <v>13202.6</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>330</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>5340</v>
       </c>
       <c r="M13" t="n">
-        <v>870</v>
+        <v>2430</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15273,10 +15273,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>33330</v>
+        <v>56070</v>
       </c>
       <c r="Q13" t="n">
-        <v>1237.87</v>
+        <v>12827.9</v>
       </c>
     </row>
     <row r="14">
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1080</v>
+        <v>6390</v>
       </c>
       <c r="M14" t="n">
+        <v>270</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>150</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>60</v>
-      </c>
       <c r="P14" t="n">
-        <v>22530</v>
+        <v>40500</v>
       </c>
       <c r="Q14" t="n">
-        <v>1214.32</v>
+        <v>12583.88</v>
       </c>
     </row>
     <row r="15">
@@ -15367,10 +15367,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>2730</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -15379,10 +15379,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>7080</v>
+        <v>13560</v>
       </c>
       <c r="Q15" t="n">
-        <v>506.33</v>
+        <v>5247.04</v>
       </c>
     </row>
     <row r="16">
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q16" t="n">
-        <v>180.01</v>
+        <v>1865.43</v>
       </c>
     </row>
     <row r="17">
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15488,7 +15488,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37.39</v>
+        <v>387.43</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.71</v>
+        <v>111.02</v>
       </c>
     </row>
     <row r="19">
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3574.8</v>
+        <v>3909.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>18.54</v>
       </c>
       <c r="L5" t="n">
-        <v>38537.1</v>
+        <v>38770.2</v>
       </c>
       <c r="M5" t="n">
-        <v>190.8</v>
+        <v>148.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2569.5</v>
+        <v>3015</v>
       </c>
       <c r="P5" t="n">
-        <v>828</v>
+        <v>667.8</v>
       </c>
       <c r="Q5" t="n">
         <v>2317.06</v>
@@ -16170,7 +16170,7 @@
         <v>1435.5</v>
       </c>
       <c r="H6" t="n">
-        <v>530.1</v>
+        <v>820.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16182,19 +16182,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>24886.2</v>
+        <v>26151.6</v>
       </c>
       <c r="M6" t="n">
-        <v>268.8</v>
+        <v>748.8</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4260</v>
+        <v>5205</v>
       </c>
       <c r="P6" t="n">
-        <v>5652</v>
+        <v>5346</v>
       </c>
       <c r="Q6" t="n">
         <v>18633.04</v>
@@ -16223,7 +16223,7 @@
         <v>1129.5</v>
       </c>
       <c r="H7" t="n">
-        <v>153.3</v>
+        <v>350.4</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -16235,19 +16235,19 @@
         <v>1.91</v>
       </c>
       <c r="L7" t="n">
-        <v>18684</v>
+        <v>23508</v>
       </c>
       <c r="M7" t="n">
-        <v>861</v>
+        <v>4105.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3433.5</v>
+        <v>4431</v>
       </c>
       <c r="P7" t="n">
-        <v>9877.5</v>
+        <v>10567.5</v>
       </c>
       <c r="Q7" t="n">
         <v>4591.4</v>
@@ -16276,7 +16276,7 @@
         <v>643.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>2.21</v>
       </c>
       <c r="L8" t="n">
-        <v>6304.8</v>
+        <v>14824.8</v>
       </c>
       <c r="M8" t="n">
-        <v>379.5</v>
+        <v>9058.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>864</v>
+        <v>1512</v>
       </c>
       <c r="P8" t="n">
-        <v>13919.4</v>
+        <v>16005.6</v>
       </c>
       <c r="Q8" t="n">
         <v>1149.79</v>
@@ -16341,19 +16341,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3086.1</v>
+        <v>19998.9</v>
       </c>
       <c r="M9" t="n">
-        <v>231</v>
+        <v>7938</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>66</v>
       </c>
       <c r="P9" t="n">
-        <v>19125</v>
+        <v>30675</v>
       </c>
       <c r="Q9" t="n">
         <v>282.54</v>
@@ -16394,19 +16394,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2937</v>
+        <v>20452.2</v>
       </c>
       <c r="M10" t="n">
-        <v>306</v>
+        <v>5584.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>22822.5</v>
+        <v>40774.5</v>
       </c>
       <c r="Q10" t="n">
         <v>176.66</v>
@@ -16435,7 +16435,7 @@
         <v>270</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -16447,10 +16447,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2430</v>
+        <v>20040</v>
       </c>
       <c r="M11" t="n">
-        <v>162</v>
+        <v>1809</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15930</v>
+        <v>29322</v>
       </c>
       <c r="Q11" t="n">
         <v>63.17</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1110</v>
+        <v>9360</v>
       </c>
       <c r="M12" t="n">
-        <v>142.5</v>
+        <v>741</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14310</v>
+        <v>18510</v>
       </c>
       <c r="Q12" t="n">
         <v>30.47</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>480</v>
+        <v>3930</v>
       </c>
       <c r="M13" t="n">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12360</v>
+        <v>30000</v>
       </c>
       <c r="Q13" t="n">
         <v>10.04</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>3540</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5370</v>
+        <v>12630</v>
       </c>
       <c r="Q14" t="n">
         <v>8.26</v>
@@ -16659,7 +16659,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>750</v>
+        <v>1440</v>
       </c>
       <c r="Q15" t="n">
         <v>2.12</v>
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q16" t="n">
         <v>0.22</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>20376360</v>
+        <v>22284720</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>900034.02</v>
       </c>
       <c r="L5" t="n">
-        <v>6936678</v>
+        <v>6978636</v>
       </c>
       <c r="M5" t="n">
-        <v>66780</v>
+        <v>52080</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>436815</v>
+        <v>512550</v>
       </c>
       <c r="P5" t="n">
-        <v>53820</v>
+        <v>43407</v>
       </c>
       <c r="Q5" t="n">
         <v>1390233.56</v>
@@ -17462,7 +17462,7 @@
         <v>77517</v>
       </c>
       <c r="H6" t="n">
-        <v>3021570</v>
+        <v>4678560</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17474,19 +17474,19 @@
         <v>443122.06</v>
       </c>
       <c r="L6" t="n">
-        <v>4479516</v>
+        <v>4707288</v>
       </c>
       <c r="M6" t="n">
-        <v>94080</v>
+        <v>262080</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>724200</v>
+        <v>884850</v>
       </c>
       <c r="P6" t="n">
-        <v>367380</v>
+        <v>347490</v>
       </c>
       <c r="Q6" t="n">
         <v>11179825.74</v>
@@ -17515,7 +17515,7 @@
         <v>60993</v>
       </c>
       <c r="H7" t="n">
-        <v>873810</v>
+        <v>1997280</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -17527,19 +17527,19 @@
         <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3363120</v>
+        <v>4231440</v>
       </c>
       <c r="M7" t="n">
-        <v>301350</v>
+        <v>1436925</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>583695</v>
+        <v>753270</v>
       </c>
       <c r="P7" t="n">
-        <v>642037.5</v>
+        <v>686887.5</v>
       </c>
       <c r="Q7" t="n">
         <v>2754841.54</v>
@@ -17568,7 +17568,7 @@
         <v>34749</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1134864</v>
+        <v>2668464</v>
       </c>
       <c r="M8" t="n">
-        <v>132825</v>
+        <v>3170475</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>146880</v>
+        <v>257040</v>
       </c>
       <c r="P8" t="n">
-        <v>904761</v>
+        <v>1040364</v>
       </c>
       <c r="Q8" t="n">
         <v>689872.14</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>555498</v>
+        <v>3599802</v>
       </c>
       <c r="M9" t="n">
-        <v>80850</v>
+        <v>2778300</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>11220</v>
       </c>
       <c r="P9" t="n">
-        <v>1243125</v>
+        <v>1993875</v>
       </c>
       <c r="Q9" t="n">
         <v>169522.63</v>
@@ -17686,19 +17686,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>528660</v>
+        <v>3681396</v>
       </c>
       <c r="M10" t="n">
-        <v>107100</v>
+        <v>1954575</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3570</v>
       </c>
       <c r="P10" t="n">
-        <v>1483462.5</v>
+        <v>2650342.5</v>
       </c>
       <c r="Q10" t="n">
         <v>105997.68</v>
@@ -17727,7 +17727,7 @@
         <v>14580</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -17739,10 +17739,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>437400</v>
+        <v>3607200</v>
       </c>
       <c r="M11" t="n">
-        <v>56700</v>
+        <v>633150</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1035450</v>
+        <v>1905930</v>
       </c>
       <c r="Q11" t="n">
         <v>37899.36</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>199800</v>
+        <v>1684800</v>
       </c>
       <c r="M12" t="n">
-        <v>49875</v>
+        <v>259350</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>930150</v>
+        <v>1203150</v>
       </c>
       <c r="Q12" t="n">
         <v>18280.08</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>86400</v>
+        <v>707400</v>
       </c>
       <c r="M13" t="n">
-        <v>115500</v>
+        <v>157500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>803400</v>
+        <v>1950000</v>
       </c>
       <c r="Q13" t="n">
         <v>6026.4</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>86400</v>
+        <v>637200</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>349050</v>
+        <v>820950</v>
       </c>
       <c r="Q14" t="n">
         <v>4955.04</v>
@@ -17951,7 +17951,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>48750</v>
+        <v>93600</v>
       </c>
       <c r="Q15" t="n">
         <v>1272.24</v>
@@ -18004,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3900</v>
+        <v>7800</v>
       </c>
       <c r="Q16" t="n">
         <v>133.92</v>
@@ -18648,7 +18648,7 @@
         <v>46710</v>
       </c>
       <c r="H4" t="n">
-        <v>3840</v>
+        <v>4320</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>166350</v>
+        <v>203070</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2790</v>
+        <v>3150</v>
       </c>
       <c r="O4" t="n">
-        <v>42390</v>
+        <v>51150</v>
       </c>
       <c r="P4" t="n">
-        <v>5220</v>
+        <v>3630</v>
       </c>
       <c r="Q4" t="n">
-        <v>14649.98</v>
+        <v>167864.4</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>9060</v>
       </c>
       <c r="H5" t="n">
-        <v>780</v>
+        <v>1290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>41790</v>
+        <v>59400</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>630</v>
+        <v>1350</v>
       </c>
       <c r="O5" t="n">
-        <v>16890</v>
+        <v>23820</v>
       </c>
       <c r="P5" t="n">
-        <v>4110</v>
+        <v>7980</v>
       </c>
       <c r="Q5" t="n">
-        <v>2872.37</v>
+        <v>32912.55</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>510</v>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7950</v>
+        <v>12510</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O6" t="n">
-        <v>2370</v>
+        <v>4080</v>
       </c>
       <c r="P6" t="n">
-        <v>2550</v>
+        <v>4710</v>
       </c>
       <c r="Q6" t="n">
-        <v>250.3</v>
+        <v>2868.03</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>480</v>
+        <v>1980</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18831,10 +18831,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2760</v>
+        <v>7680</v>
       </c>
       <c r="Q7" t="n">
-        <v>71.70999999999999</v>
+        <v>821.7</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>360</v>
+        <v>1440</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="9">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>280.8</v>
+        <v>464.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>2.65</v>
       </c>
       <c r="L5" t="n">
-        <v>8775.9</v>
+        <v>12474</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.3</v>
+        <v>13.5</v>
       </c>
       <c r="O5" t="n">
-        <v>844.5</v>
+        <v>1191</v>
       </c>
       <c r="P5" t="n">
-        <v>82.2</v>
+        <v>159.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>143.62</v>
+        <v>1645.63</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>25.5</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2941.5</v>
+        <v>4628.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>592.5</v>
+        <v>1020</v>
       </c>
       <c r="P6" t="n">
-        <v>382.5</v>
+        <v>706.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>187.73</v>
+        <v>2151.02</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>288</v>
+        <v>1188</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20123,10 +20123,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>690</v>
+        <v>1920</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.37</v>
+        <v>657.36</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>42.6</v>
+        <v>127.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>136.8</v>
+        <v>547.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="9">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1600560</v>
+        <v>2647080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>128576.29</v>
       </c>
       <c r="L5" t="n">
-        <v>1579662</v>
+        <v>2245320</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1071</v>
+        <v>2295</v>
       </c>
       <c r="O5" t="n">
-        <v>143565</v>
+        <v>202470</v>
       </c>
       <c r="P5" t="n">
-        <v>5343</v>
+        <v>10374</v>
       </c>
       <c r="Q5" t="n">
-        <v>86171.03999999999</v>
+        <v>987376.5</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>1377</v>
       </c>
       <c r="H6" t="n">
-        <v>682290</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>529470</v>
+        <v>833166</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="O6" t="n">
-        <v>100725</v>
+        <v>173400</v>
       </c>
       <c r="P6" t="n">
-        <v>24862.5</v>
+        <v>45922.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>112635.36</v>
+        <v>1290613.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51840</v>
+        <v>213840</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21415,10 +21415,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>44850</v>
+        <v>124800</v>
       </c>
       <c r="Q7" t="n">
-        <v>34421.76</v>
+        <v>394416</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7668</v>
+        <v>23004</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8892</v>
+        <v>35568</v>
       </c>
       <c r="Q8" t="n">
-        <v>886.46</v>
+        <v>10157.4</v>
       </c>
     </row>
     <row r="9">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>16200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>68208480</v>
+        <v>80397360</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -22589,22 +22589,22 @@
         <v>2378661.33</v>
       </c>
       <c r="L5" t="n">
-        <v>25587576</v>
+        <v>29099574</v>
       </c>
       <c r="M5" t="n">
-        <v>207480</v>
+        <v>346920</v>
       </c>
       <c r="N5" t="n">
-        <v>23919</v>
+        <v>29937</v>
       </c>
       <c r="O5" t="n">
-        <v>1454520</v>
+        <v>1759500</v>
       </c>
       <c r="P5" t="n">
-        <v>111657</v>
+        <v>86190</v>
       </c>
       <c r="Q5" t="n">
-        <v>3899700.18</v>
+        <v>40412215.57</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>300510</v>
       </c>
       <c r="H6" t="n">
-        <v>19786410</v>
+        <v>26706780</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>1181658.82</v>
       </c>
       <c r="L6" t="n">
-        <v>18157824</v>
+        <v>21828150</v>
       </c>
       <c r="M6" t="n">
-        <v>337680</v>
+        <v>896280</v>
       </c>
       <c r="N6" t="n">
-        <v>31620</v>
+        <v>70380</v>
       </c>
       <c r="O6" t="n">
-        <v>2724675</v>
+        <v>3684750</v>
       </c>
       <c r="P6" t="n">
-        <v>824557.5</v>
+        <v>645840</v>
       </c>
       <c r="Q6" t="n">
-        <v>31938915.6</v>
+        <v>330979891.5</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>343359</v>
       </c>
       <c r="H7" t="n">
-        <v>3370410</v>
+        <v>5991840</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -22695,22 +22695,22 @@
         <v>247829.82</v>
       </c>
       <c r="L7" t="n">
-        <v>12917880</v>
+        <v>17450640</v>
       </c>
       <c r="M7" t="n">
-        <v>995925</v>
+        <v>3777900</v>
       </c>
       <c r="N7" t="n">
-        <v>2856</v>
+        <v>12495</v>
       </c>
       <c r="O7" t="n">
-        <v>1144185</v>
+        <v>2229465</v>
       </c>
       <c r="P7" t="n">
-        <v>1411312.5</v>
+        <v>1522950</v>
       </c>
       <c r="Q7" t="n">
-        <v>16416931.39</v>
+        <v>170127071.28</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>887679</v>
       </c>
       <c r="H8" t="n">
-        <v>145350</v>
+        <v>872100</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22748,22 +22748,22 @@
         <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>5122224</v>
+        <v>9144090</v>
       </c>
       <c r="M8" t="n">
-        <v>895125</v>
+        <v>5959800</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>314415</v>
+        <v>817020</v>
       </c>
       <c r="P8" t="n">
-        <v>1930305</v>
+        <v>2232633</v>
       </c>
       <c r="Q8" t="n">
-        <v>10234471.07</v>
+        <v>106058833.24</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>352512</v>
       </c>
       <c r="H9" t="n">
-        <v>684000</v>
+        <v>1881000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>1806462</v>
+        <v>6477894</v>
       </c>
       <c r="M9" t="n">
-        <v>514500</v>
+        <v>5688900</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>19635</v>
+        <v>207570</v>
       </c>
       <c r="P9" t="n">
-        <v>2580825</v>
+        <v>4070625</v>
       </c>
       <c r="Q9" t="n">
-        <v>4640178.68</v>
+        <v>48085722.6</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>100440</v>
       </c>
       <c r="H10" t="n">
-        <v>684000</v>
+        <v>2394000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1581174</v>
+        <v>6161292</v>
       </c>
       <c r="M10" t="n">
-        <v>928200</v>
+        <v>3766350</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3570</v>
+        <v>10710</v>
       </c>
       <c r="P10" t="n">
-        <v>2910570</v>
+        <v>5047087.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2009469.6</v>
+        <v>20823939</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>51840</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22907,22 +22907,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>777600</v>
+        <v>5038200</v>
       </c>
       <c r="M11" t="n">
-        <v>75600</v>
+        <v>1275750</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4335</v>
+        <v>13005</v>
       </c>
       <c r="P11" t="n">
-        <v>2281500</v>
+        <v>3567915</v>
       </c>
       <c r="Q11" t="n">
-        <v>1062454.32</v>
+        <v>11010111.3</v>
       </c>
     </row>
     <row r="12">
@@ -22960,22 +22960,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>399600</v>
+        <v>2640600</v>
       </c>
       <c r="M12" t="n">
-        <v>79800</v>
+        <v>1725675</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P12" t="n">
-        <v>2416050</v>
+        <v>3289650</v>
       </c>
       <c r="Q12" t="n">
-        <v>764415.36</v>
+        <v>7921562.4</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>17820</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>156600</v>
+        <v>961200</v>
       </c>
       <c r="M13" t="n">
-        <v>304500</v>
+        <v>850500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2166450</v>
+        <v>3644550</v>
       </c>
       <c r="Q13" t="n">
-        <v>742720.3199999999</v>
+        <v>7696738.8</v>
       </c>
     </row>
     <row r="14">
@@ -23066,22 +23066,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>194400</v>
+        <v>1150200</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>94500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P14" t="n">
-        <v>1464450</v>
+        <v>2632500</v>
       </c>
       <c r="Q14" t="n">
-        <v>728591.76</v>
+        <v>7550325.9</v>
       </c>
     </row>
     <row r="15">
@@ -23119,10 +23119,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5400</v>
+        <v>491400</v>
       </c>
       <c r="M15" t="n">
-        <v>10500</v>
+        <v>126000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -23131,10 +23131,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>460200</v>
+        <v>881400</v>
       </c>
       <c r="Q15" t="n">
-        <v>303797.52</v>
+        <v>3148224.3</v>
       </c>
     </row>
     <row r="16">
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>70200</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3900</v>
+        <v>7800</v>
       </c>
       <c r="Q16" t="n">
-        <v>108006.48</v>
+        <v>1119260.7</v>
       </c>
     </row>
     <row r="17">
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23240,7 +23240,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22431.6</v>
+        <v>232456.5</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6428.16</v>
+        <v>66614.39999999999</v>
       </c>
     </row>
     <row r="19">
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>133.92</v>
+        <v>1387.8</v>
       </c>
     </row>
     <row r="20">
@@ -23816,7 +23816,7 @@
         <v>97230</v>
       </c>
       <c r="H4" t="n">
-        <v>5490</v>
+        <v>7320</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>74</v>
       </c>
       <c r="L4" t="n">
-        <v>244530</v>
+        <v>279870</v>
       </c>
       <c r="M4" t="n">
-        <v>21960</v>
+        <v>50460</v>
       </c>
       <c r="N4" t="n">
-        <v>13260</v>
+        <v>18900</v>
       </c>
       <c r="O4" t="n">
-        <v>27780</v>
+        <v>36450</v>
       </c>
       <c r="P4" t="n">
-        <v>8280</v>
+        <v>5790</v>
       </c>
       <c r="Q4" t="n">
-        <v>35754.72</v>
+        <v>350536.5</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>92220</v>
       </c>
       <c r="H5" t="n">
-        <v>1320</v>
+        <v>1920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>55</v>
       </c>
       <c r="L5" t="n">
-        <v>195660</v>
+        <v>228450</v>
       </c>
       <c r="M5" t="n">
-        <v>7200</v>
+        <v>24570</v>
       </c>
       <c r="N5" t="n">
-        <v>3150</v>
+        <v>3900</v>
       </c>
       <c r="O5" t="n">
-        <v>23070</v>
+        <v>32220</v>
       </c>
       <c r="P5" t="n">
-        <v>16140</v>
+        <v>8610</v>
       </c>
       <c r="Q5" t="n">
-        <v>35473.54</v>
+        <v>347779.8</v>
       </c>
     </row>
     <row r="6">
@@ -23934,22 +23934,22 @@
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>107700</v>
+        <v>130350</v>
       </c>
       <c r="M6" t="n">
-        <v>2910</v>
+        <v>9540</v>
       </c>
       <c r="N6" t="n">
-        <v>840</v>
+        <v>1740</v>
       </c>
       <c r="O6" t="n">
-        <v>8130</v>
+        <v>15120</v>
       </c>
       <c r="P6" t="n">
-        <v>16560</v>
+        <v>9990</v>
       </c>
       <c r="Q6" t="n">
-        <v>22407.65</v>
+        <v>219682.8</v>
       </c>
     </row>
     <row r="7">
@@ -23987,22 +23987,22 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>47910</v>
+        <v>65610</v>
       </c>
       <c r="M7" t="n">
-        <v>2070</v>
+        <v>6720</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1260</v>
+        <v>5460</v>
       </c>
       <c r="P7" t="n">
-        <v>16380</v>
+        <v>18630</v>
       </c>
       <c r="Q7" t="n">
-        <v>12660.23</v>
+        <v>124119.9</v>
       </c>
     </row>
     <row r="8">
@@ -24040,22 +24040,22 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>16440</v>
+        <v>25080</v>
       </c>
       <c r="M8" t="n">
-        <v>2340</v>
+        <v>5790</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>180</v>
+        <v>1710</v>
       </c>
       <c r="P8" t="n">
-        <v>13020</v>
+        <v>13260</v>
       </c>
       <c r="Q8" t="n">
-        <v>7488.77</v>
+        <v>73419.3</v>
       </c>
     </row>
     <row r="9">
@@ -24093,22 +24093,22 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>3630</v>
+        <v>9300</v>
       </c>
       <c r="M9" t="n">
-        <v>780</v>
+        <v>3840</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="P9" t="n">
-        <v>16500</v>
+        <v>17790</v>
       </c>
       <c r="Q9" t="n">
-        <v>2835.7</v>
+        <v>27801</v>
       </c>
     </row>
     <row r="10">
@@ -24146,22 +24146,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1980</v>
+        <v>5130</v>
       </c>
       <c r="M10" t="n">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
-        <v>13890</v>
+        <v>18390</v>
       </c>
       <c r="Q10" t="n">
-        <v>841.8099999999999</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="11">
@@ -24199,22 +24199,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>690</v>
+        <v>4470</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P11" t="n">
-        <v>15210</v>
+        <v>16650</v>
       </c>
       <c r="Q11" t="n">
-        <v>343.61</v>
+        <v>3368.7</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>330</v>
+        <v>2730</v>
       </c>
       <c r="M12" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>16200</v>
+        <v>18300</v>
       </c>
       <c r="Q12" t="n">
-        <v>200.86</v>
+        <v>1969.2</v>
       </c>
     </row>
     <row r="13">
@@ -24305,10 +24305,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
       <c r="M13" t="n">
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -24317,10 +24317,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>18270</v>
+        <v>21060</v>
       </c>
       <c r="Q13" t="n">
-        <v>167.53</v>
+        <v>1642.5</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>1410</v>
+      </c>
+      <c r="M14" t="n">
         <v>60</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>150</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>60</v>
-      </c>
       <c r="P14" t="n">
-        <v>16650</v>
+        <v>26850</v>
       </c>
       <c r="Q14" t="n">
-        <v>121.91</v>
+        <v>1195.2</v>
       </c>
     </row>
     <row r="15">
@@ -24411,10 +24411,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>1020</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6330</v>
+        <v>12120</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.28</v>
+        <v>375.3</v>
       </c>
     </row>
     <row r="16">
@@ -24467,7 +24467,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24479,7 +24479,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.77</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="17">
@@ -24520,7 +24520,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24532,7 +24532,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="18">
@@ -24573,7 +24573,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24585,7 +24585,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.78</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="19">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>475.2</v>
+        <v>691.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>18.21</v>
       </c>
       <c r="L5" t="n">
-        <v>41088.6</v>
+        <v>47974.5</v>
       </c>
       <c r="M5" t="n">
-        <v>144</v>
+        <v>491.4</v>
       </c>
       <c r="N5" t="n">
-        <v>31.5</v>
+        <v>39</v>
       </c>
       <c r="O5" t="n">
-        <v>1153.5</v>
+        <v>1611</v>
       </c>
       <c r="P5" t="n">
-        <v>322.8</v>
+        <v>172.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1773.68</v>
+        <v>17388.99</v>
       </c>
     </row>
     <row r="6">
@@ -25226,22 +25226,22 @@
         <v>13.69</v>
       </c>
       <c r="L6" t="n">
-        <v>39849</v>
+        <v>48229.5</v>
       </c>
       <c r="M6" t="n">
-        <v>232.8</v>
+        <v>763.2</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="O6" t="n">
-        <v>2032.5</v>
+        <v>3780</v>
       </c>
       <c r="P6" t="n">
-        <v>2484</v>
+        <v>1498.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>16805.73</v>
+        <v>164762.1</v>
       </c>
     </row>
     <row r="7">
@@ -25279,22 +25279,22 @@
         <v>3.19</v>
       </c>
       <c r="L7" t="n">
-        <v>28746</v>
+        <v>39366</v>
       </c>
       <c r="M7" t="n">
-        <v>724.5</v>
+        <v>2352</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>441</v>
+        <v>1911</v>
       </c>
       <c r="P7" t="n">
-        <v>4095</v>
+        <v>4657.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>10128.18</v>
+        <v>99295.92</v>
       </c>
     </row>
     <row r="8">
@@ -25332,22 +25332,22 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>11672.4</v>
+        <v>17806.8</v>
       </c>
       <c r="M8" t="n">
-        <v>1287</v>
+        <v>3184.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>81</v>
+        <v>769.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4947.6</v>
+        <v>5038.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>7114.33</v>
+        <v>69748.34</v>
       </c>
     </row>
     <row r="9">
@@ -25385,22 +25385,22 @@
         <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>2940.3</v>
+        <v>7533</v>
       </c>
       <c r="M9" t="n">
-        <v>546</v>
+        <v>2688</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>511.5</v>
       </c>
       <c r="P9" t="n">
-        <v>8250</v>
+        <v>8895</v>
       </c>
       <c r="Q9" t="n">
-        <v>2750.63</v>
+        <v>26966.97</v>
       </c>
     </row>
     <row r="10">
@@ -25438,22 +25438,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1762.2</v>
+        <v>4565.7</v>
       </c>
       <c r="M10" t="n">
-        <v>76.5</v>
+        <v>306</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>11806.5</v>
+        <v>15631.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>841.8099999999999</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="11">
@@ -25491,22 +25491,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>690</v>
+        <v>4470</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>25.5</v>
+        <v>76.5</v>
       </c>
       <c r="P11" t="n">
-        <v>13689</v>
+        <v>14985</v>
       </c>
       <c r="Q11" t="n">
-        <v>343.61</v>
+        <v>3368.7</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>330</v>
+        <v>2730</v>
       </c>
       <c r="M12" t="n">
-        <v>85.5</v>
+        <v>57</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>16200</v>
+        <v>18300</v>
       </c>
       <c r="Q12" t="n">
-        <v>200.86</v>
+        <v>1969.2</v>
       </c>
     </row>
     <row r="13">
@@ -25597,10 +25597,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
       <c r="M13" t="n">
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -25609,10 +25609,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>18270</v>
+        <v>21060</v>
       </c>
       <c r="Q13" t="n">
-        <v>167.54</v>
+        <v>1642.5</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>1410</v>
+      </c>
+      <c r="M14" t="n">
         <v>60</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>150</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>60</v>
-      </c>
       <c r="P14" t="n">
-        <v>16650</v>
+        <v>26850</v>
       </c>
       <c r="Q14" t="n">
-        <v>121.91</v>
+        <v>1195.2</v>
       </c>
     </row>
     <row r="15">
@@ -25703,10 +25703,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>1020</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -25715,10 +25715,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6330</v>
+        <v>12120</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.28</v>
+        <v>375.3</v>
       </c>
     </row>
     <row r="16">
@@ -25759,7 +25759,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25771,7 +25771,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.77</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="17">
@@ -25812,7 +25812,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25824,7 +25824,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="18">
@@ -25865,7 +25865,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25877,7 +25877,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.78</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="19">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2708640</v>
+        <v>3939840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>883961.98</v>
       </c>
       <c r="L5" t="n">
-        <v>7395948</v>
+        <v>8635410</v>
       </c>
       <c r="M5" t="n">
-        <v>50400</v>
+        <v>171990</v>
       </c>
       <c r="N5" t="n">
-        <v>5355</v>
+        <v>6630</v>
       </c>
       <c r="O5" t="n">
-        <v>196095</v>
+        <v>273870</v>
       </c>
       <c r="P5" t="n">
-        <v>20982</v>
+        <v>11193</v>
       </c>
       <c r="Q5" t="n">
-        <v>1064206.19</v>
+        <v>10433394</v>
       </c>
     </row>
     <row r="6">
@@ -26518,22 +26518,22 @@
         <v>664683.08</v>
       </c>
       <c r="L6" t="n">
-        <v>7172820</v>
+        <v>8681310</v>
       </c>
       <c r="M6" t="n">
-        <v>81480</v>
+        <v>267120</v>
       </c>
       <c r="N6" t="n">
-        <v>7140</v>
+        <v>14790</v>
       </c>
       <c r="O6" t="n">
-        <v>345525</v>
+        <v>642600</v>
       </c>
       <c r="P6" t="n">
-        <v>161460</v>
+        <v>97402.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>10083440.52</v>
+        <v>98857260</v>
       </c>
     </row>
     <row r="7">
@@ -26571,22 +26571,22 @@
         <v>154893.64</v>
       </c>
       <c r="L7" t="n">
-        <v>5174280</v>
+        <v>7085880</v>
       </c>
       <c r="M7" t="n">
-        <v>253575</v>
+        <v>823200</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>74970</v>
+        <v>324870</v>
       </c>
       <c r="P7" t="n">
-        <v>266175</v>
+        <v>302737.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>6076910.3</v>
+        <v>59577552</v>
       </c>
     </row>
     <row r="8">
@@ -26624,22 +26624,22 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>2101032</v>
+        <v>3205224</v>
       </c>
       <c r="M8" t="n">
-        <v>450450</v>
+        <v>1114575</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>13770</v>
+        <v>130815</v>
       </c>
       <c r="P8" t="n">
-        <v>321594</v>
+        <v>327522</v>
       </c>
       <c r="Q8" t="n">
-        <v>4268598.1</v>
+        <v>41849001</v>
       </c>
     </row>
     <row r="9">
@@ -26677,22 +26677,22 @@
         <v>38990.47</v>
       </c>
       <c r="L9" t="n">
-        <v>529254</v>
+        <v>1355940</v>
       </c>
       <c r="M9" t="n">
-        <v>191100</v>
+        <v>940800</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>86955</v>
       </c>
       <c r="P9" t="n">
-        <v>536250</v>
+        <v>578175</v>
       </c>
       <c r="Q9" t="n">
-        <v>1650378.56</v>
+        <v>16180182</v>
       </c>
     </row>
     <row r="10">
@@ -26730,22 +26730,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>317196</v>
+        <v>821826</v>
       </c>
       <c r="M10" t="n">
-        <v>26775</v>
+        <v>107100</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3570</v>
+        <v>7140</v>
       </c>
       <c r="P10" t="n">
-        <v>767422.5</v>
+        <v>1016047.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>505083.6</v>
+        <v>4951800</v>
       </c>
     </row>
     <row r="11">
@@ -26783,22 +26783,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>124200</v>
+        <v>804600</v>
       </c>
       <c r="M11" t="n">
-        <v>9450</v>
+        <v>18900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4335</v>
+        <v>13005</v>
       </c>
       <c r="P11" t="n">
-        <v>889785</v>
+        <v>974025</v>
       </c>
       <c r="Q11" t="n">
-        <v>206164.44</v>
+        <v>2021220</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>59400</v>
+        <v>491400</v>
       </c>
       <c r="M12" t="n">
-        <v>29925</v>
+        <v>19950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P12" t="n">
-        <v>1053000</v>
+        <v>1189500</v>
       </c>
       <c r="Q12" t="n">
-        <v>120515.04</v>
+        <v>1181520</v>
       </c>
     </row>
     <row r="13">
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>27000</v>
+        <v>156600</v>
       </c>
       <c r="M13" t="n">
-        <v>189000</v>
+        <v>220500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -26901,10 +26901,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1187550</v>
+        <v>1368900</v>
       </c>
       <c r="Q13" t="n">
-        <v>100521</v>
+        <v>985500</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10800</v>
+        <v>253800</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>21000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P14" t="n">
-        <v>1082250</v>
+        <v>1745250</v>
       </c>
       <c r="Q14" t="n">
-        <v>73146.24000000001</v>
+        <v>717120</v>
       </c>
     </row>
     <row r="15">
@@ -26995,10 +26995,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5400</v>
+        <v>183600</v>
       </c>
       <c r="M15" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -27007,10 +27007,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>411450</v>
+        <v>787800</v>
       </c>
       <c r="Q15" t="n">
-        <v>22968.36</v>
+        <v>225180</v>
       </c>
     </row>
     <row r="16">
@@ -27051,7 +27051,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27063,7 +27063,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2864.16</v>
+        <v>28080</v>
       </c>
     </row>
     <row r="17">
@@ -27104,7 +27104,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27116,7 +27116,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>660.96</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="18">
@@ -27157,7 +27157,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27169,7 +27169,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3470.04</v>
+        <v>34020</v>
       </c>
     </row>
     <row r="19">
@@ -27692,7 +27692,7 @@
         <v>106110</v>
       </c>
       <c r="H4" t="n">
-        <v>28230</v>
+        <v>30270</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27704,7 +27704,7 @@
         <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>292560</v>
+        <v>345420</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>81510</v>
+        <v>85920</v>
       </c>
       <c r="P4" t="n">
-        <v>1470</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>26830.15</v>
+        <v>373584.42</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>47940</v>
       </c>
       <c r="H5" t="n">
-        <v>15270</v>
+        <v>17280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>105540</v>
+        <v>119400</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>39300</v>
+        <v>47640</v>
       </c>
       <c r="P5" t="n">
-        <v>2580</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
-        <v>8902.57</v>
+        <v>123959.88</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>6720</v>
       </c>
       <c r="H6" t="n">
-        <v>1050</v>
+        <v>1410</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18930</v>
+        <v>25230</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>13560</v>
+        <v>18720</v>
       </c>
       <c r="P6" t="n">
-        <v>4260</v>
+        <v>450</v>
       </c>
       <c r="Q6" t="n">
-        <v>739.16</v>
+        <v>10292.04</v>
       </c>
     </row>
     <row r="7">
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4320</v>
+        <v>6150</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3480</v>
+        <v>10920</v>
       </c>
       <c r="P7" t="n">
-        <v>4950</v>
+        <v>1230</v>
       </c>
       <c r="Q7" t="n">
-        <v>119.16</v>
+        <v>1659.24</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>780</v>
+        <v>2520</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>900</v>
+        <v>4500</v>
       </c>
       <c r="P8" t="n">
-        <v>5910</v>
+        <v>5190</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.16</v>
+        <v>364.32</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>330</v>
+        <v>1980</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>840</v>
       </c>
       <c r="P9" t="n">
-        <v>4770</v>
+        <v>10680</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.17</v>
+        <v>127.71</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>1350</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2310</v>
+        <v>7200</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.99</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>720</v>
+        <v>2670</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="12">
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5497.2</v>
+        <v>6220.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>22163.4</v>
+        <v>25074</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1965</v>
+        <v>2382</v>
       </c>
       <c r="P5" t="n">
-        <v>51.6</v>
+        <v>1.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>445.13</v>
+        <v>6197.99</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>336</v>
       </c>
       <c r="H6" t="n">
-        <v>598.5</v>
+        <v>803.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7004.1</v>
+        <v>9335.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3390</v>
+        <v>4680</v>
       </c>
       <c r="P6" t="n">
-        <v>639</v>
+        <v>67.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>554.37</v>
+        <v>7719.03</v>
       </c>
     </row>
     <row r="7">
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2592</v>
+        <v>3690</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1218</v>
+        <v>3822</v>
       </c>
       <c r="P7" t="n">
-        <v>1237.5</v>
+        <v>307.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>95.33</v>
+        <v>1327.39</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>58.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.5</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>553.8</v>
+        <v>1789.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>405</v>
+        <v>2025</v>
       </c>
       <c r="P8" t="n">
-        <v>2245.8</v>
+        <v>1972.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.86</v>
+        <v>346.1</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>267.3</v>
+        <v>1603.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>462</v>
       </c>
       <c r="P9" t="n">
-        <v>2385</v>
+        <v>5340</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.9</v>
+        <v>123.88</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.7</v>
+        <v>1201.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29326,10 +29326,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1963.5</v>
+        <v>6120</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.99</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>648</v>
+        <v>2403</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="12">
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>31334040</v>
+        <v>35458560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>257152.58</v>
       </c>
       <c r="L5" t="n">
-        <v>3989412</v>
+        <v>4513320</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>334050</v>
+        <v>404940</v>
       </c>
       <c r="P5" t="n">
-        <v>3354</v>
+        <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>267077.2</v>
+        <v>3718796.4</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>18144</v>
       </c>
       <c r="H6" t="n">
-        <v>3411450</v>
+        <v>4581090</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1260738</v>
+        <v>1680318</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>576300</v>
+        <v>795600</v>
       </c>
       <c r="P6" t="n">
-        <v>41535</v>
+        <v>4387.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>332620.02</v>
+        <v>4631418</v>
       </c>
     </row>
     <row r="7">
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>466560</v>
+        <v>664200</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>207060</v>
+        <v>649740</v>
       </c>
       <c r="P7" t="n">
-        <v>80437.5</v>
+        <v>19987.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>57198.53</v>
+        <v>796435.2</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>3159</v>
       </c>
       <c r="H8" t="n">
-        <v>145350</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>99684</v>
+        <v>322056</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>68850</v>
+        <v>344250</v>
       </c>
       <c r="P8" t="n">
-        <v>145977</v>
+        <v>128193</v>
       </c>
       <c r="Q8" t="n">
-        <v>14913.94</v>
+        <v>207662.4</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>171000</v>
+        <v>1197000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48114</v>
+        <v>288684</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>78540</v>
       </c>
       <c r="P9" t="n">
-        <v>155025</v>
+        <v>347100</v>
       </c>
       <c r="Q9" t="n">
-        <v>5338.05</v>
+        <v>74327.22</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4806</v>
+        <v>216270</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30618,10 +30618,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>127627.5</v>
+        <v>397800</v>
       </c>
       <c r="Q10" t="n">
-        <v>1194.48</v>
+        <v>16632</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>42120</v>
+        <v>156195</v>
       </c>
       <c r="Q11" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="12">
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7800</v>
+        <v>39000</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13">
